--- a/public/seed/cedar-residence.xlsx
+++ b/public/seed/cedar-residence.xlsx
@@ -696,16 +696,16 @@
         <v>2</v>
       </c>
       <c r="F2">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="G2" t="str">
         <v>no</v>
       </c>
       <c r="H2">
-        <v>1075</v>
+        <v>1125</v>
       </c>
       <c r="I2">
-        <v>1075</v>
+        <v>1125</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -731,16 +731,16 @@
         <v>1</v>
       </c>
       <c r="F3">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G3" t="str">
         <v>no</v>
       </c>
       <c r="H3">
-        <v>900</v>
+        <v>975</v>
       </c>
       <c r="I3">
-        <v>900</v>
+        <v>975</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -766,16 +766,16 @@
         <v>1</v>
       </c>
       <c r="F4">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="G4" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="H4">
-        <v>800</v>
+        <v>775</v>
       </c>
       <c r="I4">
-        <v>800</v>
+        <v>775</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -801,16 +801,16 @@
         <v>2</v>
       </c>
       <c r="F5">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G5" t="str">
-        <v>yes</v>
+        <v>no</v>
       </c>
       <c r="H5">
-        <v>1200</v>
+        <v>1150</v>
       </c>
       <c r="I5">
-        <v>1200</v>
+        <v>1150</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -836,16 +836,16 @@
         <v>1</v>
       </c>
       <c r="F6">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G6" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="H6">
-        <v>925</v>
+        <v>1000</v>
       </c>
       <c r="I6">
-        <v>925</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -871,16 +871,16 @@
         <v>1</v>
       </c>
       <c r="F7">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G7" t="str">
         <v>no</v>
       </c>
       <c r="H7">
-        <v>775</v>
+        <v>800</v>
       </c>
       <c r="I7">
-        <v>775</v>
+        <v>800</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -906,16 +906,16 @@
         <v>2</v>
       </c>
       <c r="F8">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="G8" t="str">
         <v>yes</v>
       </c>
       <c r="H8">
-        <v>1200</v>
+        <v>1175</v>
       </c>
       <c r="I8">
-        <v>1200</v>
+        <v>1175</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -941,16 +941,16 @@
         <v>1</v>
       </c>
       <c r="F9">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="G9" t="str">
-        <v>yes</v>
+        <v>no</v>
       </c>
       <c r="H9">
-        <v>925</v>
+        <v>1025</v>
       </c>
       <c r="I9">
-        <v>925</v>
+        <v>1025</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -976,16 +976,16 @@
         <v>1</v>
       </c>
       <c r="F10">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="G10" t="str">
         <v>yes</v>
       </c>
       <c r="H10">
-        <v>775</v>
+        <v>825</v>
       </c>
       <c r="I10">
-        <v>775</v>
+        <v>825</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -1011,16 +1011,16 @@
         <v>2</v>
       </c>
       <c r="F11">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G11" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="H11">
-        <v>1125</v>
+        <v>1250</v>
       </c>
       <c r="I11">
-        <v>1125</v>
+        <v>1250</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -1046,16 +1046,16 @@
         <v>1</v>
       </c>
       <c r="F12">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G12" t="str">
         <v>no</v>
       </c>
       <c r="H12">
-        <v>1000</v>
+        <v>1050</v>
       </c>
       <c r="I12">
-        <v>1000</v>
+        <v>1050</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -1081,16 +1081,16 @@
         <v>1</v>
       </c>
       <c r="F13">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G13" t="str">
         <v>no</v>
       </c>
       <c r="H13">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="I13">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -1116,16 +1116,16 @@
         <v>2</v>
       </c>
       <c r="F14">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="G14" t="str">
         <v>no</v>
       </c>
       <c r="H14">
-        <v>1250</v>
+        <v>1150</v>
       </c>
       <c r="I14">
-        <v>1250</v>
+        <v>1150</v>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -1151,7 +1151,7 @@
         <v>1</v>
       </c>
       <c r="F15">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G15" t="str">
         <v>no</v>
@@ -1186,16 +1186,16 @@
         <v>1</v>
       </c>
       <c r="F16">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="G16" t="str">
         <v>no</v>
       </c>
       <c r="H16">
-        <v>825</v>
+        <v>875</v>
       </c>
       <c r="I16">
-        <v>825</v>
+        <v>875</v>
       </c>
       <c r="J16" t="str">
         <v/>
@@ -1221,16 +1221,16 @@
         <v>2</v>
       </c>
       <c r="F17">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="G17" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="H17">
-        <v>1200</v>
+        <v>1275</v>
       </c>
       <c r="I17">
-        <v>1200</v>
+        <v>1275</v>
       </c>
       <c r="J17" t="str">
         <v/>
@@ -1256,16 +1256,16 @@
         <v>1</v>
       </c>
       <c r="F18">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="G18" t="str">
         <v>no</v>
       </c>
       <c r="H18">
-        <v>1050</v>
+        <v>1000</v>
       </c>
       <c r="I18">
-        <v>1050</v>
+        <v>1000</v>
       </c>
       <c r="J18" t="str">
         <v/>
@@ -1291,16 +1291,16 @@
         <v>1</v>
       </c>
       <c r="F19">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="G19" t="str">
-        <v>yes</v>
+        <v>no</v>
       </c>
       <c r="H19">
-        <v>900</v>
+        <v>850</v>
       </c>
       <c r="I19">
-        <v>900</v>
+        <v>850</v>
       </c>
       <c r="J19" t="str">
         <v/>
@@ -1370,34 +1370,34 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Marie</v>
+        <v>Jad</v>
       </c>
       <c r="B2" t="str">
-        <v>Rizk</v>
+        <v>Dagher</v>
       </c>
       <c r="C2" t="str">
-        <v>+961 81 170 216</v>
+        <v>+961 70 489 845</v>
       </c>
       <c r="D2" t="str">
-        <v>marie.rizk@example.com</v>
+        <v>jad.dagher@example.com</v>
       </c>
       <c r="E2" t="str">
         <v>Lebanese</v>
       </c>
       <c r="F2" t="str">
-        <v>passport</v>
+        <v>national_id</v>
       </c>
       <c r="G2" t="str">
-        <v>RL6979454</v>
+        <v>LB-6900604</v>
       </c>
       <c r="H2" t="str">
-        <v>Accountant</v>
+        <v>Designer</v>
       </c>
       <c r="I2" t="str">
-        <v>Rafic Rizk</v>
+        <v/>
       </c>
       <c r="J2" t="str">
-        <v/>
+        <v>+961 71 534 988</v>
       </c>
       <c r="K2" t="str">
         <v/>
@@ -1405,16 +1405,16 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Nabil</v>
+        <v>Rima</v>
       </c>
       <c r="B3" t="str">
-        <v>Osseiran</v>
+        <v>Fares</v>
       </c>
       <c r="C3" t="str">
-        <v>+961 71 235 156</v>
+        <v>+961 78 642 109</v>
       </c>
       <c r="D3" t="str">
-        <v>nabil.osseiran@example.com</v>
+        <v>rima.fares@example.com</v>
       </c>
       <c r="E3" t="str">
         <v>Lebanese</v>
@@ -1423,16 +1423,16 @@
         <v>national_id</v>
       </c>
       <c r="G3" t="str">
-        <v>LB-8914569</v>
+        <v>LB-1685442</v>
       </c>
       <c r="H3" t="str">
-        <v>Designer</v>
+        <v>Bank officer</v>
       </c>
       <c r="I3" t="str">
-        <v>Dima Osseiran</v>
+        <v/>
       </c>
       <c r="J3" t="str">
-        <v>+961 3 759 930</v>
+        <v>+961 79 751 636</v>
       </c>
       <c r="K3" t="str">
         <v/>
@@ -1440,16 +1440,16 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Sandra</v>
+        <v>Antoine</v>
       </c>
       <c r="B4" t="str">
-        <v>Hajj</v>
+        <v>Baydoun</v>
       </c>
       <c r="C4" t="str">
-        <v>+961 70 361 683</v>
+        <v>+961 70 108 759</v>
       </c>
       <c r="D4" t="str">
-        <v>sandra.hajj@example.com</v>
+        <v>antoine.baydoun@example.com</v>
       </c>
       <c r="E4" t="str">
         <v>Lebanese</v>
@@ -1458,16 +1458,16 @@
         <v>national_id</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>LB-7737871</v>
       </c>
       <c r="H4" t="str">
-        <v>Consultant</v>
+        <v>Journalist</v>
       </c>
       <c r="I4" t="str">
-        <v>Salim Hajj</v>
+        <v/>
       </c>
       <c r="J4" t="str">
-        <v>+961 71 947 538</v>
+        <v>+961 76 953 284</v>
       </c>
       <c r="K4" t="str">
         <v/>
@@ -1475,16 +1475,16 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Maria</v>
+        <v>Antoine</v>
       </c>
       <c r="B5" t="str">
-        <v>Chehab</v>
+        <v>Nasrallah</v>
       </c>
       <c r="C5" t="str">
-        <v>+961 78 442 534</v>
+        <v>+961 78 258 933</v>
       </c>
       <c r="D5" t="str">
-        <v>maria.chehab@example.com</v>
+        <v>antoine.nasrallah@example.com</v>
       </c>
       <c r="E5" t="str">
         <v>Lebanese</v>
@@ -1493,16 +1493,16 @@
         <v>national_id</v>
       </c>
       <c r="G5" t="str">
-        <v>LB-2236731</v>
+        <v>LB-4126818</v>
       </c>
       <c r="H5" t="str">
-        <v>Engineer</v>
+        <v>Bank officer</v>
       </c>
       <c r="I5" t="str">
-        <v/>
+        <v>Nada Nasrallah</v>
       </c>
       <c r="J5" t="str">
-        <v>+961 76 570 797</v>
+        <v>+961 79 386 582</v>
       </c>
       <c r="K5" t="str">
         <v/>
@@ -1510,34 +1510,34 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Tamara</v>
+        <v>Rony</v>
       </c>
       <c r="B6" t="str">
-        <v>Nakhle</v>
+        <v>Hajj</v>
       </c>
       <c r="C6" t="str">
-        <v>+961 70 219 593</v>
+        <v>+961 81 751 494</v>
       </c>
       <c r="D6" t="str">
-        <v>tamara.nakhle@example.com</v>
+        <v>rony.hajj@example.com</v>
       </c>
       <c r="E6" t="str">
-        <v>Lebanese</v>
+        <v>Jordanian</v>
       </c>
       <c r="F6" t="str">
-        <v>national_id</v>
+        <v>passport</v>
       </c>
       <c r="G6" t="str">
-        <v>LB-8270749</v>
+        <v>RL4787623</v>
       </c>
       <c r="H6" t="str">
         <v>Bank officer</v>
       </c>
       <c r="I6" t="str">
-        <v>Fouad Nakhle</v>
+        <v/>
       </c>
       <c r="J6" t="str">
-        <v/>
+        <v>+961 76 784 663</v>
       </c>
       <c r="K6" t="str">
         <v/>
@@ -1545,34 +1545,34 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Jessica</v>
+        <v>Maya</v>
       </c>
       <c r="B7" t="str">
-        <v>Makhlouf</v>
+        <v>Rizk</v>
       </c>
       <c r="C7" t="str">
-        <v>+961 81 284 501</v>
+        <v>+961 79 533 713</v>
       </c>
       <c r="D7" t="str">
-        <v>jessica.makhlouf@example.com</v>
+        <v>maya.rizk@example.com</v>
       </c>
       <c r="E7" t="str">
-        <v>Syrian</v>
+        <v>Egyptian</v>
       </c>
       <c r="F7" t="str">
         <v>passport</v>
       </c>
       <c r="G7" t="str">
-        <v>RL9994819</v>
+        <v>RL6775325</v>
       </c>
       <c r="H7" t="str">
-        <v>Nurse</v>
+        <v>Accountant</v>
       </c>
       <c r="I7" t="str">
-        <v/>
+        <v>Khaled Rizk</v>
       </c>
       <c r="J7" t="str">
-        <v>+961 81 334 111</v>
+        <v/>
       </c>
       <c r="K7" t="str">
         <v/>
@@ -1580,34 +1580,34 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Nicolas</v>
+        <v>Roy</v>
       </c>
       <c r="B8" t="str">
-        <v>Hobeika</v>
+        <v>Fakhoury</v>
       </c>
       <c r="C8" t="str">
-        <v>+961 78 477 783</v>
+        <v>+961 71 801 321</v>
       </c>
       <c r="D8" t="str">
-        <v>nicolas.hobeika@example.com</v>
+        <v>roy.fakhoury@example.com</v>
       </c>
       <c r="E8" t="str">
         <v>Lebanese</v>
       </c>
       <c r="F8" t="str">
-        <v>national_id</v>
+        <v>passport</v>
       </c>
       <c r="G8" t="str">
-        <v>LB-5823991</v>
+        <v>RL4085610</v>
       </c>
       <c r="H8" t="str">
-        <v>Consultant</v>
+        <v>Designer</v>
       </c>
       <c r="I8" t="str">
-        <v/>
+        <v>Marie Fakhoury</v>
       </c>
       <c r="J8" t="str">
-        <v/>
+        <v>+961 70 164 924</v>
       </c>
       <c r="K8" t="str">
         <v/>
@@ -1615,31 +1615,31 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Tamara</v>
+        <v>Ali</v>
       </c>
       <c r="B9" t="str">
-        <v>Kassab</v>
+        <v>Nassar</v>
       </c>
       <c r="C9" t="str">
-        <v>+961 3 478 366</v>
+        <v>+961 78 828 106</v>
       </c>
       <c r="D9" t="str">
-        <v>tamara.kassab@example.com</v>
+        <v>ali.nassar@example.com</v>
       </c>
       <c r="E9" t="str">
-        <v>Lebanese</v>
+        <v>Canadian</v>
       </c>
       <c r="F9" t="str">
-        <v>national_id</v>
+        <v>passport</v>
       </c>
       <c r="G9" t="str">
-        <v>LB-6824243</v>
+        <v>RL7106746</v>
       </c>
       <c r="H9" t="str">
-        <v>Restaurant owner</v>
+        <v>Consultant</v>
       </c>
       <c r="I9" t="str">
-        <v>Lara Kassab</v>
+        <v/>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -1650,16 +1650,16 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Imad</v>
+        <v>Sandra</v>
       </c>
       <c r="B10" t="str">
-        <v>Farah</v>
+        <v>Baydoun</v>
       </c>
       <c r="C10" t="str">
-        <v>+961 78 848 533</v>
+        <v>+961 79 438 693</v>
       </c>
       <c r="D10" t="str">
-        <v>imad.farah@example.com</v>
+        <v>sandra.baydoun@example.com</v>
       </c>
       <c r="E10" t="str">
         <v>Lebanese</v>
@@ -1668,16 +1668,16 @@
         <v>national_id</v>
       </c>
       <c r="G10" t="str">
-        <v>LB-1334610</v>
+        <v>LB-6019906</v>
       </c>
       <c r="H10" t="str">
-        <v>Bank officer</v>
+        <v>Architect</v>
       </c>
       <c r="I10" t="str">
-        <v>Ghassan Farah</v>
+        <v>Kamal Baydoun</v>
       </c>
       <c r="J10" t="str">
-        <v>+961 78 279 949</v>
+        <v>+961 70 550 287</v>
       </c>
       <c r="K10" t="str">
         <v/>
@@ -1685,34 +1685,34 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Roy</v>
+        <v>Imad</v>
       </c>
       <c r="B11" t="str">
-        <v>Fakhoury</v>
+        <v>Maalouf</v>
       </c>
       <c r="C11" t="str">
-        <v>+961 71 801 321</v>
+        <v>+961 78 872 553</v>
       </c>
       <c r="D11" t="str">
-        <v>roy.fakhoury@example.com</v>
+        <v>imad.maalouf@example.com</v>
       </c>
       <c r="E11" t="str">
         <v>Lebanese</v>
       </c>
       <c r="F11" t="str">
-        <v>passport</v>
+        <v>national_id</v>
       </c>
       <c r="G11" t="str">
-        <v>RL4085610</v>
+        <v>LB-8511653</v>
       </c>
       <c r="H11" t="str">
-        <v>Designer</v>
+        <v>Teacher</v>
       </c>
       <c r="I11" t="str">
-        <v>Marie Fakhoury</v>
+        <v>Sara Maalouf</v>
       </c>
       <c r="J11" t="str">
-        <v>+961 70 164 924</v>
+        <v/>
       </c>
       <c r="K11" t="str">
         <v/>
@@ -1720,34 +1720,34 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Ali</v>
+        <v>Walid</v>
       </c>
       <c r="B12" t="str">
-        <v>Nassar</v>
+        <v>Ayoub</v>
       </c>
       <c r="C12" t="str">
-        <v>+961 78 828 106</v>
+        <v>+961 70 701 949</v>
       </c>
       <c r="D12" t="str">
-        <v>ali.nassar@example.com</v>
+        <v>walid.ayoub@example.com</v>
       </c>
       <c r="E12" t="str">
-        <v>Canadian</v>
+        <v>Syrian</v>
       </c>
       <c r="F12" t="str">
         <v>passport</v>
       </c>
       <c r="G12" t="str">
-        <v>RL7106746</v>
+        <v>RL1245733</v>
       </c>
       <c r="H12" t="str">
-        <v>Consultant</v>
+        <v>Nurse</v>
       </c>
       <c r="I12" t="str">
-        <v/>
+        <v>Rita Ayoub</v>
       </c>
       <c r="J12" t="str">
-        <v/>
+        <v>+961 78 647 728</v>
       </c>
       <c r="K12" t="str">
         <v/>
@@ -1755,34 +1755,34 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Christine</v>
+        <v>Tarek</v>
       </c>
       <c r="B13" t="str">
-        <v>Saade</v>
+        <v>Kfoury</v>
       </c>
       <c r="C13" t="str">
-        <v>+961 71 601 199</v>
+        <v>+961 81 524 789</v>
       </c>
       <c r="D13" t="str">
-        <v>christine.saade@example.com</v>
+        <v>tarek.kfoury@example.com</v>
       </c>
       <c r="E13" t="str">
         <v>Lebanese</v>
       </c>
       <c r="F13" t="str">
-        <v>national_id</v>
+        <v>passport</v>
       </c>
       <c r="G13" t="str">
-        <v>LB-3852143</v>
+        <v>RL5683314</v>
       </c>
       <c r="H13" t="str">
         <v>Bank officer</v>
       </c>
       <c r="I13" t="str">
-        <v>Nadine Saade</v>
+        <v>Pascale Kfoury</v>
       </c>
       <c r="J13" t="str">
-        <v>+961 81 711 622</v>
+        <v>+961 70 267 964</v>
       </c>
       <c r="K13" t="str">
         <v/>
@@ -1790,31 +1790,31 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Mariam</v>
+        <v>Tala</v>
       </c>
       <c r="B14" t="str">
-        <v>Makhlouf</v>
+        <v>Chehab</v>
       </c>
       <c r="C14" t="str">
-        <v>+961 76 851 237</v>
+        <v>+961 70 969 500</v>
       </c>
       <c r="D14" t="str">
-        <v>mariam.makhlouf@example.com</v>
+        <v>tala.chehab@example.com</v>
       </c>
       <c r="E14" t="str">
         <v>Lebanese</v>
       </c>
       <c r="F14" t="str">
-        <v>national_id</v>
+        <v>passport</v>
       </c>
       <c r="G14" t="str">
-        <v>LB-6790836</v>
+        <v>RL5435856</v>
       </c>
       <c r="H14" t="str">
-        <v>Sales manager</v>
+        <v>Lawyer</v>
       </c>
       <c r="I14" t="str">
-        <v>Josiane Makhlouf</v>
+        <v>Pascale Chehab</v>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -1825,34 +1825,34 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Nicolas</v>
+        <v>Selim</v>
       </c>
       <c r="B15" t="str">
-        <v>Hijazi</v>
+        <v>Kassab</v>
       </c>
       <c r="C15" t="str">
-        <v>+961 70 124 242</v>
+        <v>+961 3 800 428</v>
       </c>
       <c r="D15" t="str">
-        <v>nicolas.hijazi@example.com</v>
+        <v>selim.kassab@example.com</v>
       </c>
       <c r="E15" t="str">
         <v>Lebanese</v>
       </c>
       <c r="F15" t="str">
-        <v>passport</v>
+        <v>national_id</v>
       </c>
       <c r="G15" t="str">
-        <v>RL5267604</v>
+        <v>LB-4604729</v>
       </c>
       <c r="H15" t="str">
-        <v>Designer</v>
+        <v>Physician</v>
       </c>
       <c r="I15" t="str">
-        <v>Rima Hijazi</v>
+        <v>Fadi Kassab</v>
       </c>
       <c r="J15" t="str">
-        <v>+961 78 526 749</v>
+        <v/>
       </c>
       <c r="K15" t="str">
         <v/>
@@ -1931,22 +1931,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>CR-103-01</v>
+        <v>CR-203-01</v>
       </c>
       <c r="B2" t="str">
         <v>CR</v>
       </c>
       <c r="C2" t="str">
-        <v>103</v>
+        <v>203</v>
       </c>
       <c r="D2" t="str">
-        <v>+961 81 170 216</v>
+        <v>+961 70 489 845</v>
       </c>
       <c r="E2" t="str">
-        <v>today+286d-12m</v>
+        <v>today+98d-24m</v>
       </c>
       <c r="F2" t="str">
-        <v>today+286d</v>
+        <v>today+98d</v>
       </c>
       <c r="G2">
         <v>800</v>
@@ -1955,10 +1955,10 @@
         <v>800</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="J2" t="str">
-        <v>cash</v>
+        <v>bank_transfer</v>
       </c>
       <c r="K2" t="str">
         <v/>
@@ -1975,34 +1975,34 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>CR-102-01</v>
+        <v>CR-103-01</v>
       </c>
       <c r="B3" t="str">
         <v>CR</v>
       </c>
       <c r="C3" t="str">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D3" t="str">
-        <v>+961 71 235 156</v>
+        <v>+961 78 642 109</v>
       </c>
       <c r="E3" t="str">
-        <v>today+187d-12m</v>
+        <v>today+130d-24m</v>
       </c>
       <c r="F3" t="str">
-        <v>today+187d</v>
+        <v>today+130d</v>
       </c>
       <c r="G3">
-        <v>900</v>
+        <v>775</v>
       </c>
       <c r="H3">
-        <v>900</v>
+        <v>775</v>
       </c>
       <c r="I3">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J3" t="str">
-        <v>bank_transfer</v>
+        <v>cheque</v>
       </c>
       <c r="K3" t="str">
         <v/>
@@ -2019,31 +2019,31 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>CR-501-01</v>
+        <v>CR-202-01</v>
       </c>
       <c r="B4" t="str">
         <v>CR</v>
       </c>
       <c r="C4" t="str">
-        <v>501</v>
+        <v>202</v>
       </c>
       <c r="D4" t="str">
-        <v>+961 70 361 683</v>
+        <v>+961 70 108 759</v>
       </c>
       <c r="E4" t="str">
-        <v>today+174d-12m</v>
+        <v>today+181d-24m</v>
       </c>
       <c r="F4" t="str">
-        <v>today+174d</v>
+        <v>today+181d</v>
       </c>
       <c r="G4">
-        <v>1250</v>
+        <v>1000</v>
       </c>
       <c r="H4">
-        <v>1250</v>
+        <v>1000</v>
       </c>
       <c r="I4">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="J4" t="str">
         <v>bank_transfer</v>
@@ -2063,22 +2063,22 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>CR-401-01</v>
+        <v>CR-101-01</v>
       </c>
       <c r="B5" t="str">
         <v>CR</v>
       </c>
       <c r="C5" t="str">
-        <v>401</v>
+        <v>101</v>
       </c>
       <c r="D5" t="str">
-        <v>+961 78 442 534</v>
+        <v>+961 78 258 933</v>
       </c>
       <c r="E5" t="str">
-        <v>today+134d-12m</v>
+        <v>today+258d-12m</v>
       </c>
       <c r="F5" t="str">
-        <v>today+134d</v>
+        <v>today+258d</v>
       </c>
       <c r="G5">
         <v>1125</v>
@@ -2087,7 +2087,7 @@
         <v>1125</v>
       </c>
       <c r="I5">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J5" t="str">
         <v>cash</v>
@@ -2107,34 +2107,34 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>CR-203-01</v>
+        <v>CR-102-01</v>
       </c>
       <c r="B6" t="str">
         <v>CR</v>
       </c>
       <c r="C6" t="str">
-        <v>203</v>
+        <v>102</v>
       </c>
       <c r="D6" t="str">
-        <v>+961 70 219 593</v>
+        <v>+961 81 751 494</v>
       </c>
       <c r="E6" t="str">
-        <v>today+102d-24m</v>
+        <v>today+268d-24m</v>
       </c>
       <c r="F6" t="str">
-        <v>today+102d</v>
+        <v>today+268d</v>
       </c>
       <c r="G6">
-        <v>775</v>
+        <v>975</v>
       </c>
       <c r="H6">
-        <v>775</v>
+        <v>975</v>
       </c>
       <c r="I6">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="J6" t="str">
-        <v>cash</v>
+        <v>bank_transfer</v>
       </c>
       <c r="K6" t="str">
         <v/>
@@ -2151,34 +2151,34 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>CR-503-01</v>
+        <v>CR-302-01</v>
       </c>
       <c r="B7" t="str">
         <v>CR</v>
       </c>
       <c r="C7" t="str">
-        <v>503</v>
+        <v>302</v>
       </c>
       <c r="D7" t="str">
-        <v>+961 81 284 501</v>
+        <v>+961 79 533 713</v>
       </c>
       <c r="E7" t="str">
-        <v>today+189d-12m</v>
+        <v>today+162d-12m</v>
       </c>
       <c r="F7" t="str">
-        <v>today+189d</v>
+        <v>today+162d</v>
       </c>
       <c r="G7">
-        <v>825</v>
+        <v>1025</v>
       </c>
       <c r="H7">
-        <v>825</v>
+        <v>1025</v>
       </c>
       <c r="I7">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J7" t="str">
-        <v>bank_transfer</v>
+        <v>cheque</v>
       </c>
       <c r="K7" t="str">
         <v/>
@@ -2195,34 +2195,34 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>CR-403-01</v>
+        <v>CR-503-01</v>
       </c>
       <c r="B8" t="str">
         <v>CR</v>
       </c>
       <c r="C8" t="str">
-        <v>403</v>
+        <v>503</v>
       </c>
       <c r="D8" t="str">
-        <v>+961 78 477 783</v>
+        <v>+961 71 801 321</v>
       </c>
       <c r="E8" t="str">
-        <v>today+227d-24m</v>
+        <v>today+189d-12m</v>
       </c>
       <c r="F8" t="str">
-        <v>today+227d</v>
+        <v>today+189d</v>
       </c>
       <c r="G8">
-        <v>800</v>
+        <v>875</v>
       </c>
       <c r="H8">
-        <v>800</v>
+        <v>875</v>
       </c>
       <c r="I8">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="J8" t="str">
-        <v>bank_transfer</v>
+        <v>cash</v>
       </c>
       <c r="K8" t="str">
         <v/>
@@ -2239,31 +2239,31 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>CR-303-01</v>
+        <v>CR-603-01</v>
       </c>
       <c r="B9" t="str">
         <v>CR</v>
       </c>
       <c r="C9" t="str">
-        <v>303</v>
+        <v>603</v>
       </c>
       <c r="D9" t="str">
-        <v>+961 3 478 366</v>
+        <v>+961 78 828 106</v>
       </c>
       <c r="E9" t="str">
-        <v>today+230d-12m</v>
+        <v>today+197d-24m</v>
       </c>
       <c r="F9" t="str">
-        <v>today+230d</v>
+        <v>today+197d</v>
       </c>
       <c r="G9">
-        <v>775</v>
+        <v>850</v>
       </c>
       <c r="H9">
-        <v>775</v>
+        <v>850</v>
       </c>
       <c r="I9">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="J9" t="str">
         <v>bank_transfer</v>
@@ -2283,28 +2283,28 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>CR-602-01</v>
+        <v>CR-401-01</v>
       </c>
       <c r="B10" t="str">
         <v>CR</v>
       </c>
       <c r="C10" t="str">
-        <v>602</v>
+        <v>401</v>
       </c>
       <c r="D10" t="str">
-        <v>+961 78 848 533</v>
+        <v>+961 79 438 693</v>
       </c>
       <c r="E10" t="str">
-        <v>today+162d-12m</v>
+        <v>today+317d-12m</v>
       </c>
       <c r="F10" t="str">
-        <v>today+162d</v>
+        <v>today+317d</v>
       </c>
       <c r="G10">
-        <v>1050</v>
+        <v>1250</v>
       </c>
       <c r="H10">
-        <v>1050</v>
+        <v>1250</v>
       </c>
       <c r="I10">
         <v>17</v>
@@ -2327,34 +2327,34 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>CR-301-01</v>
+        <v>CR-402-01</v>
       </c>
       <c r="B11" t="str">
         <v>CR</v>
       </c>
       <c r="C11" t="str">
-        <v>301</v>
+        <v>402</v>
       </c>
       <c r="D11" t="str">
-        <v>+961 71 801 321</v>
+        <v>+961 78 872 553</v>
       </c>
       <c r="E11" t="str">
-        <v>today+189d-12m</v>
+        <v>today+141d-12m</v>
       </c>
       <c r="F11" t="str">
-        <v>today+189d</v>
+        <v>today+141d</v>
       </c>
       <c r="G11">
-        <v>1200</v>
+        <v>1050</v>
       </c>
       <c r="H11">
-        <v>1200</v>
+        <v>1050</v>
       </c>
       <c r="I11">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J11" t="str">
-        <v>cash</v>
+        <v>bank_transfer</v>
       </c>
       <c r="K11" t="str">
         <v/>
@@ -2371,31 +2371,31 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>CR-101-01</v>
+        <v>CR-502-01</v>
       </c>
       <c r="B12" t="str">
         <v>CR</v>
       </c>
       <c r="C12" t="str">
-        <v>101</v>
+        <v>502</v>
       </c>
       <c r="D12" t="str">
-        <v>+961 78 828 106</v>
+        <v>+961 70 701 949</v>
       </c>
       <c r="E12" t="str">
-        <v>today+197d-24m</v>
+        <v>today+188d-12m</v>
       </c>
       <c r="F12" t="str">
-        <v>today+197d</v>
+        <v>today+188d</v>
       </c>
       <c r="G12">
-        <v>1075</v>
+        <v>1050</v>
       </c>
       <c r="H12">
-        <v>1075</v>
+        <v>1050</v>
       </c>
       <c r="I12">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J12" t="str">
         <v>bank_transfer</v>
@@ -2415,34 +2415,34 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>CR-202-01</v>
+        <v>CR-403-01</v>
       </c>
       <c r="B13" t="str">
         <v>CR</v>
       </c>
       <c r="C13" t="str">
-        <v>202</v>
+        <v>403</v>
       </c>
       <c r="D13" t="str">
-        <v>+961 71 601 199</v>
+        <v>+961 81 524 789</v>
       </c>
       <c r="E13" t="str">
-        <v>today+270d-12m</v>
+        <v>today+99d-24m</v>
       </c>
       <c r="F13" t="str">
-        <v>today+270d</v>
+        <v>today+99d</v>
       </c>
       <c r="G13">
-        <v>925</v>
+        <v>900</v>
       </c>
       <c r="H13">
-        <v>925</v>
+        <v>900</v>
       </c>
       <c r="I13">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="J13" t="str">
-        <v>bank_transfer</v>
+        <v>cash</v>
       </c>
       <c r="K13" t="str">
         <v/>
@@ -2459,31 +2459,31 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>CR-201-01</v>
+        <v>CR-303-01</v>
       </c>
       <c r="B14" t="str">
         <v>CR</v>
       </c>
       <c r="C14" t="str">
-        <v>201</v>
+        <v>303</v>
       </c>
       <c r="D14" t="str">
-        <v>+961 76 851 237</v>
+        <v>+961 70 969 500</v>
       </c>
       <c r="E14" t="str">
-        <v>today+115d-12m</v>
+        <v>today+208d-12m</v>
       </c>
       <c r="F14" t="str">
-        <v>today+115d</v>
+        <v>today+208d</v>
       </c>
       <c r="G14">
-        <v>1200</v>
+        <v>825</v>
       </c>
       <c r="H14">
-        <v>1200</v>
+        <v>825</v>
       </c>
       <c r="I14">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="J14" t="str">
         <v>bank_transfer</v>
@@ -2503,34 +2503,34 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>CR-603-01</v>
+        <v>CR-602-01</v>
       </c>
       <c r="B15" t="str">
         <v>CR</v>
       </c>
       <c r="C15" t="str">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D15" t="str">
-        <v>+961 70 124 242</v>
+        <v>+961 3 800 428</v>
       </c>
       <c r="E15" t="str">
-        <v>today+192d-12m</v>
+        <v>today+120d-12m</v>
       </c>
       <c r="F15" t="str">
-        <v>today+192d</v>
+        <v>today+120d</v>
       </c>
       <c r="G15">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="H15">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="I15">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J15" t="str">
-        <v>bank_transfer</v>
+        <v>cash</v>
       </c>
       <c r="K15" t="str">
         <v/>
@@ -2590,7 +2590,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>+961 78 442 534</v>
+        <v>+961 70 108 759</v>
       </c>
       <c r="B2" t="str">
         <v>id</v>
@@ -2599,16 +2599,16 @@
         <v>National ID</v>
       </c>
       <c r="D2" t="str">
-        <v>maria-chehab-id.pdf</v>
+        <v>antoine-baydoun-id.pdf</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>today-8y</v>
+        <v>today-5y</v>
       </c>
       <c r="G2" t="str">
-        <v>today+44d</v>
+        <v>today+2y</v>
       </c>
     </row>
   </sheetData>

--- a/public/seed/cedar-residence.xlsx
+++ b/public/seed/cedar-residence.xlsx
@@ -8,8 +8,22 @@
     <sheet name="Units" sheetId="3" r:id="rId3"/>
     <sheet name="Tenants" sheetId="4" r:id="rId4"/>
     <sheet name="Contracts" sheetId="5" r:id="rId5"/>
-    <sheet name="Documents" sheetId="6" r:id="rId6"/>
-    <sheet name="Payments" sheetId="7" r:id="rId7"/>
+    <sheet name="Suppliers" sheetId="6" r:id="rId6"/>
+    <sheet name="Assets" sheetId="7" r:id="rId7"/>
+    <sheet name="WorkOrders" sheetId="8" r:id="rId8"/>
+    <sheet name="PreventivePlans" sheetId="9" r:id="rId9"/>
+    <sheet name="Expenses" sheetId="10" r:id="rId10"/>
+    <sheet name="Budgets" sheetId="11" r:id="rId11"/>
+    <sheet name="Deposits" sheetId="12" r:id="rId12"/>
+    <sheet name="Meters" sheetId="13" r:id="rId13"/>
+    <sheet name="Readings" sheetId="14" r:id="rId14"/>
+    <sheet name="CommonCharges" sheetId="15" r:id="rId15"/>
+    <sheet name="Inspections" sheetId="16" r:id="rId16"/>
+    <sheet name="Renovations" sheetId="17" r:id="rId17"/>
+    <sheet name="Parking" sheetId="18" r:id="rId18"/>
+    <sheet name="Keys" sheetId="19" r:id="rId19"/>
+    <sheet name="Documents" sheetId="20" r:id="rId20"/>
+    <sheet name="Payments" sheetId="21" r:id="rId21"/>
   </sheets>
 </workbook>
 </file>
@@ -403,7 +417,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A27"/>
   <cols>
     <col min="1" max="1" width="120.83203125" customWidth="1"/>
   </cols>
@@ -420,7 +434,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>One tab per entity. Row 1 is the header and must not be edited. Rows below the header are your data; the sample rows in this file can be deleted.</v>
+        <v>One tab per entity. Row 1 is the header and must not be edited. Rows below the header are your data; the sample rows in this file can be deleted. Every tab except Properties is optional.</v>
       </c>
     </row>
     <row r="4">
@@ -430,7 +444,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Import order is Properties → Units → Tenants → Contracts → Documents. A row may reference something defined in the same file or already in the system.</v>
+        <v>Import order is Properties → Units → Tenants → Contracts → Suppliers → Assets → WorkOrders → PreventivePlans → Expenses → Budgets → Deposits → Meters → Readings → CommonCharges → Inspections → Renovations → Parking → Keys → Documents. A row may reference something defined in the same file or already in the system.</v>
       </c>
     </row>
     <row r="6">
@@ -445,104 +459,928 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v xml:space="preserve">  Properties: property_code</v>
+        <v xml:space="preserve">  Properties: property_code · Units: property_code + unit_number · Tenants: phone (or id_number) · Contracts: contract_number</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v xml:space="preserve">  Units: property_code + unit_number</v>
+        <v xml:space="preserve">  Suppliers: name · Assets: property_code + name · WorkOrders: number · PreventivePlans: property_code + asset_name + maintenance_type</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v xml:space="preserve">  Tenants: phone (or id_number)</v>
+        <v xml:space="preserve">  Expenses: property_code + expense_date + description · Budgets: property_code + period + category · Deposits: contract_number</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v xml:space="preserve">  Contracts: contract_number</v>
+        <v xml:space="preserve">  Meters: meter_number · Readings: meter_number + reading_date · CommonCharges: property_code + period + category</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v xml:space="preserve">  Documents: tenant_phone + kind + file_name</v>
+        <v xml:space="preserve">  Inspections: property_code + unit_number + type + scheduled_date · Renovations: property_code + title · Parking: property_code + space_number · Keys: property_code + identifier</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v/>
+        <v xml:space="preserve">  Documents: owner + kind + file_name</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Dates: use YYYY-MM-DD. Relative tokens are also accepted and resolved on import: today, today+28d, today-8d, today-5m, today+1y.</v>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v/>
+        <v>Dates: use YYYY-MM-DD. Relative tokens are also accepted and resolved on import: today, today+28d, today-8d, today-5m, today+1y. Periods accept YYYY-MM, YYYY, today, today-1m or year.</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Units: rented / available is derived from active contracts — leave status blank unless the unit is under maintenance or reserved.</v>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v/>
+        <v>Units: rented / available is derived from active contracts — leave status blank unless the unit is under maintenance, reserved, being renovated or unavailable.</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Contracts: a monthly payment schedule is generated from start_date to end_date. Past periods are recorded as paid on time unless payment_pattern says otherwise.</v>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v xml:space="preserve">  payment_pattern entries are separated by | and refer to the payment whose due date is closest to today + N days:</v>
+        <v>Contracts: a payment schedule is generated from start_date to end_date. Past periods are recorded as paid on time unless payment_pattern says otherwise.</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v xml:space="preserve">    overdue@-8          unpaid, due 8 days ago</v>
+        <v xml:space="preserve">  payment_pattern entries are separated by | and refer to the payment whose due date is closest to today + N days:</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v xml:space="preserve">    late@-150:5         paid 5 days late, due ~150 days ago</v>
+        <v xml:space="preserve">    overdue@-8          unpaid, due 8 days ago</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v xml:space="preserve">    partial@-12:800     paid 800 of the amount due</v>
+        <v xml:space="preserve">    late@-150:5         paid 5 days late, due ~150 days ago</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v xml:space="preserve">    unpaid@+20          not yet paid (future)</v>
+        <v xml:space="preserve">    partial@-12:800     paid 800 of the amount due</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v/>
+        <v xml:space="preserve">    unpaid@+20          not yet paid (future)</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
+        <v xml:space="preserve">  A security deposit record is created for every contract; use the Deposits tab to record deductions and settlements.</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
         <v>Payments tab: shown for reference only; payments are not imported in this version.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A25"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A27"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:R6"/>
+  <cols>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="16.83203125" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
+    <col min="10" max="10" width="14.83203125" customWidth="1"/>
+    <col min="11" max="11" width="14.83203125" customWidth="1"/>
+    <col min="12" max="12" width="14.83203125" customWidth="1"/>
+    <col min="13" max="13" width="16.83203125" customWidth="1"/>
+    <col min="14" max="14" width="16.83203125" customWidth="1"/>
+    <col min="15" max="15" width="19.83203125" customWidth="1"/>
+    <col min="16" max="16" width="18.83203125" customWidth="1"/>
+    <col min="17" max="17" width="14.83203125" customWidth="1"/>
+    <col min="18" max="18" width="14.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>property_code</v>
+      </c>
+      <c r="B1" t="str">
+        <v>unit_number</v>
+      </c>
+      <c r="C1" t="str">
+        <v>supplier_name</v>
+      </c>
+      <c r="D1" t="str">
+        <v>category</v>
+      </c>
+      <c r="E1" t="str">
+        <v>amount</v>
+      </c>
+      <c r="F1" t="str">
+        <v>expense_date</v>
+      </c>
+      <c r="G1" t="str">
+        <v>due_date</v>
+      </c>
+      <c r="H1" t="str">
+        <v>payment_status</v>
+      </c>
+      <c r="I1" t="str">
+        <v>paid_date</v>
+      </c>
+      <c r="J1" t="str">
+        <v>recurring</v>
+      </c>
+      <c r="K1" t="str">
+        <v>recurrence</v>
+      </c>
+      <c r="L1" t="str">
+        <v>description</v>
+      </c>
+      <c r="M1" t="str">
+        <v>classification</v>
+      </c>
+      <c r="N1" t="str">
+        <v>invoice_number</v>
+      </c>
+      <c r="O1" t="str">
+        <v>work_order_number</v>
+      </c>
+      <c r="P1" t="str">
+        <v>renovation_title</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>asset_name</v>
+      </c>
+      <c r="R1" t="str">
+        <v>notes</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>CR</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v>Schindler Lebanon</v>
+      </c>
+      <c r="D2" t="str">
+        <v>elevator</v>
+      </c>
+      <c r="E2">
+        <v>350</v>
+      </c>
+      <c r="F2" t="str">
+        <v>today-12d</v>
+      </c>
+      <c r="G2" t="str">
+        <v>today-12d+30d</v>
+      </c>
+      <c r="H2" t="str">
+        <v>paid</v>
+      </c>
+      <c r="I2" t="str">
+        <v>today-7d</v>
+      </c>
+      <c r="J2" t="str">
+        <v>yes</v>
+      </c>
+      <c r="K2" t="str">
+        <v>quarterly</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Elevator service — Elevator 1</v>
+      </c>
+      <c r="M2" t="str">
+        <v>operating</v>
+      </c>
+      <c r="N2" t="str">
+        <v>INV-33915</v>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
+        <v>Elevator 1</v>
+      </c>
+      <c r="R2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>CR</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v>PowerGen Services</v>
+      </c>
+      <c r="D3" t="str">
+        <v>generator</v>
+      </c>
+      <c r="E3">
+        <v>400</v>
+      </c>
+      <c r="F3" t="str">
+        <v>today-52d</v>
+      </c>
+      <c r="G3" t="str">
+        <v>today-52d+30d</v>
+      </c>
+      <c r="H3" t="str">
+        <v>paid</v>
+      </c>
+      <c r="I3" t="str">
+        <v>today-46d</v>
+      </c>
+      <c r="J3" t="str">
+        <v>yes</v>
+      </c>
+      <c r="K3" t="str">
+        <v>semi_annual</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Generator service — Generator</v>
+      </c>
+      <c r="M3" t="str">
+        <v>operating</v>
+      </c>
+      <c r="N3" t="str">
+        <v>INV-17864</v>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v>Generator</v>
+      </c>
+      <c r="R3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>CR</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v>AquaTank Services</v>
+      </c>
+      <c r="D4" t="str">
+        <v>maintenance</v>
+      </c>
+      <c r="E4">
+        <v>120</v>
+      </c>
+      <c r="F4" t="str">
+        <v>today-95d</v>
+      </c>
+      <c r="G4" t="str">
+        <v>today-95d+30d</v>
+      </c>
+      <c r="H4" t="str">
+        <v>paid</v>
+      </c>
+      <c r="I4" t="str">
+        <v>today-88d</v>
+      </c>
+      <c r="J4" t="str">
+        <v>yes</v>
+      </c>
+      <c r="K4" t="str">
+        <v>semi_annual</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Pump inspection — Water pump</v>
+      </c>
+      <c r="M4" t="str">
+        <v>operating</v>
+      </c>
+      <c r="N4" t="str">
+        <v>INV-39851</v>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
+        <v>Water pump</v>
+      </c>
+      <c r="R4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>CR</v>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v>AquaTank Services</v>
+      </c>
+      <c r="D5" t="str">
+        <v>maintenance</v>
+      </c>
+      <c r="E5">
+        <v>180</v>
+      </c>
+      <c r="F5" t="str">
+        <v>today-162d</v>
+      </c>
+      <c r="G5" t="str">
+        <v>today-162d+30d</v>
+      </c>
+      <c r="H5" t="str">
+        <v>paid</v>
+      </c>
+      <c r="I5" t="str">
+        <v>today-159d</v>
+      </c>
+      <c r="J5" t="str">
+        <v>yes</v>
+      </c>
+      <c r="K5" t="str">
+        <v>semi_annual</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Tank cleaning — Roof water tank</v>
+      </c>
+      <c r="M5" t="str">
+        <v>operating</v>
+      </c>
+      <c r="N5" t="str">
+        <v>INV-46637</v>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+      <c r="Q5" t="str">
+        <v>Roof water tank</v>
+      </c>
+      <c r="R5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>CR</v>
+      </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
+      <c r="C6" t="str">
+        <v>Nakhle Electric</v>
+      </c>
+      <c r="D6" t="str">
+        <v>maintenance</v>
+      </c>
+      <c r="E6">
+        <v>200</v>
+      </c>
+      <c r="F6" t="str">
+        <v>today-174d</v>
+      </c>
+      <c r="G6" t="str">
+        <v>today-174d+30d</v>
+      </c>
+      <c r="H6" t="str">
+        <v>paid</v>
+      </c>
+      <c r="I6" t="str">
+        <v>today-163d</v>
+      </c>
+      <c r="J6" t="str">
+        <v>yes</v>
+      </c>
+      <c r="K6" t="str">
+        <v>annual</v>
+      </c>
+      <c r="L6" t="str">
+        <v>Panel thermal inspection — Main electrical panel</v>
+      </c>
+      <c r="M6" t="str">
+        <v>operating</v>
+      </c>
+      <c r="N6" t="str">
+        <v>INV-54602</v>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <v/>
+      </c>
+      <c r="Q6" t="str">
+        <v>Main electrical panel</v>
+      </c>
+      <c r="R6" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:R6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E1"/>
+  <cols>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>property_code</v>
+      </c>
+      <c r="B1" t="str">
+        <v>period</v>
+      </c>
+      <c r="C1" t="str">
+        <v>category</v>
+      </c>
+      <c r="D1" t="str">
+        <v>amount</v>
+      </c>
+      <c r="E1" t="str">
+        <v>notes</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H1"/>
+  <cols>
+    <col min="1" max="1" width="17.83203125" customWidth="1"/>
+    <col min="2" max="2" width="17.83203125" customWidth="1"/>
+    <col min="3" max="3" width="17.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="17.83203125" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>contract_number</v>
+      </c>
+      <c r="B1" t="str">
+        <v>amount_expected</v>
+      </c>
+      <c r="C1" t="str">
+        <v>amount_received</v>
+      </c>
+      <c r="D1" t="str">
+        <v>received_date</v>
+      </c>
+      <c r="E1" t="str">
+        <v>deductions</v>
+      </c>
+      <c r="F1" t="str">
+        <v>final_refund</v>
+      </c>
+      <c r="G1" t="str">
+        <v>settlement_date</v>
+      </c>
+      <c r="H1" t="str">
+        <v>notes</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G1"/>
+  <cols>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>property_code</v>
+      </c>
+      <c r="B1" t="str">
+        <v>unit_number</v>
+      </c>
+      <c r="C1" t="str">
+        <v>utility_type</v>
+      </c>
+      <c r="D1" t="str">
+        <v>meter_number</v>
+      </c>
+      <c r="E1" t="str">
+        <v>billing_method</v>
+      </c>
+      <c r="F1" t="str">
+        <v>unit_rate</v>
+      </c>
+      <c r="G1" t="str">
+        <v>unit_label</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F1"/>
+  <cols>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" customWidth="1"/>
+    <col min="4" max="4" width="17.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>meter_number</v>
+      </c>
+      <c r="B1" t="str">
+        <v>reading_date</v>
+      </c>
+      <c r="C1" t="str">
+        <v>previous_reading</v>
+      </c>
+      <c r="D1" t="str">
+        <v>current_reading</v>
+      </c>
+      <c r="E1" t="str">
+        <v>meter_reset</v>
+      </c>
+      <c r="F1" t="str">
+        <v>note</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G1"/>
+  <cols>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="19.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>property_code</v>
+      </c>
+      <c r="B1" t="str">
+        <v>period</v>
+      </c>
+      <c r="C1" t="str">
+        <v>category</v>
+      </c>
+      <c r="D1" t="str">
+        <v>total_amount</v>
+      </c>
+      <c r="E1" t="str">
+        <v>allocation_method</v>
+      </c>
+      <c r="F1" t="str">
+        <v>paid_units</v>
+      </c>
+      <c r="G1" t="str">
+        <v>notes</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L1"/>
+  <cols>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="16.83203125" customWidth="1"/>
+    <col min="7" max="7" width="16.83203125" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
+    <col min="10" max="10" width="16.83203125" customWidth="1"/>
+    <col min="11" max="11" width="14.83203125" customWidth="1"/>
+    <col min="12" max="12" width="14.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>property_code</v>
+      </c>
+      <c r="B1" t="str">
+        <v>unit_number</v>
+      </c>
+      <c r="C1" t="str">
+        <v>asset_name</v>
+      </c>
+      <c r="D1" t="str">
+        <v>tenant_phone</v>
+      </c>
+      <c r="E1" t="str">
+        <v>type</v>
+      </c>
+      <c r="F1" t="str">
+        <v>scheduled_date</v>
+      </c>
+      <c r="G1" t="str">
+        <v>completed_date</v>
+      </c>
+      <c r="H1" t="str">
+        <v>inspector</v>
+      </c>
+      <c r="I1" t="str">
+        <v>status</v>
+      </c>
+      <c r="J1" t="str">
+        <v>overall_result</v>
+      </c>
+      <c r="K1" t="str">
+        <v>items</v>
+      </c>
+      <c r="L1" t="str">
+        <v>notes</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:L1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:N1"/>
+  <cols>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="17.83203125" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" customWidth="1"/>
+    <col min="9" max="9" width="17.83203125" customWidth="1"/>
+    <col min="10" max="10" width="17.83203125" customWidth="1"/>
+    <col min="11" max="11" width="14.83203125" customWidth="1"/>
+    <col min="12" max="12" width="18.83203125" customWidth="1"/>
+    <col min="13" max="13" width="14.83203125" customWidth="1"/>
+    <col min="14" max="14" width="14.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>property_code</v>
+      </c>
+      <c r="B1" t="str">
+        <v>unit_number</v>
+      </c>
+      <c r="C1" t="str">
+        <v>title</v>
+      </c>
+      <c r="D1" t="str">
+        <v>description</v>
+      </c>
+      <c r="E1" t="str">
+        <v>project_type</v>
+      </c>
+      <c r="F1" t="str">
+        <v>budget</v>
+      </c>
+      <c r="G1" t="str">
+        <v>contractor_name</v>
+      </c>
+      <c r="H1" t="str">
+        <v>start_date</v>
+      </c>
+      <c r="I1" t="str">
+        <v>target_end_date</v>
+      </c>
+      <c r="J1" t="str">
+        <v>actual_end_date</v>
+      </c>
+      <c r="K1" t="str">
+        <v>status</v>
+      </c>
+      <c r="L1" t="str">
+        <v>progress_percent</v>
+      </c>
+      <c r="M1" t="str">
+        <v>tasks</v>
+      </c>
+      <c r="N1" t="str">
+        <v>notes</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:N1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I1"/>
+  <cols>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>property_code</v>
+      </c>
+      <c r="B1" t="str">
+        <v>space_number</v>
+      </c>
+      <c r="C1" t="str">
+        <v>unit_number</v>
+      </c>
+      <c r="D1" t="str">
+        <v>tenant_phone</v>
+      </c>
+      <c r="E1" t="str">
+        <v>vehicle_plate</v>
+      </c>
+      <c r="F1" t="str">
+        <v>paid</v>
+      </c>
+      <c r="G1" t="str">
+        <v>monthly_fee</v>
+      </c>
+      <c r="H1" t="str">
+        <v>status</v>
+      </c>
+      <c r="I1" t="str">
+        <v>notes</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J1"/>
+  <cols>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="15.83203125" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
+    <col min="10" max="10" width="14.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>property_code</v>
+      </c>
+      <c r="B1" t="str">
+        <v>unit_number</v>
+      </c>
+      <c r="C1" t="str">
+        <v>type</v>
+      </c>
+      <c r="D1" t="str">
+        <v>identifier</v>
+      </c>
+      <c r="E1" t="str">
+        <v>assigned_to</v>
+      </c>
+      <c r="F1" t="str">
+        <v>tenant_phone</v>
+      </c>
+      <c r="G1" t="str">
+        <v>issued_date</v>
+      </c>
+      <c r="H1" t="str">
+        <v>returned_date</v>
+      </c>
+      <c r="I1" t="str">
+        <v>status</v>
+      </c>
+      <c r="J1" t="str">
+        <v>notes</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:J1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:R2"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -554,6 +1392,14 @@
     <col min="8" max="8" width="14.83203125" customWidth="1"/>
     <col min="9" max="9" width="17.83203125" customWidth="1"/>
     <col min="10" max="10" width="14.83203125" customWidth="1"/>
+    <col min="11" max="11" width="14.83203125" customWidth="1"/>
+    <col min="12" max="12" width="18.83203125" customWidth="1"/>
+    <col min="13" max="13" width="18.83203125" customWidth="1"/>
+    <col min="14" max="14" width="17.83203125" customWidth="1"/>
+    <col min="15" max="15" width="20.83203125" customWidth="1"/>
+    <col min="16" max="16" width="25.83203125" customWidth="1"/>
+    <col min="17" max="17" width="18.83203125" customWidth="1"/>
+    <col min="18" max="18" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -585,6 +1431,30 @@
         <v>units_per_floor</v>
       </c>
       <c r="J1" t="str">
+        <v>type</v>
+      </c>
+      <c r="K1" t="str">
+        <v>status</v>
+      </c>
+      <c r="L1" t="str">
+        <v>acquisition_date</v>
+      </c>
+      <c r="M1" t="str">
+        <v>acquisition_cost</v>
+      </c>
+      <c r="N1" t="str">
+        <v>estimated_value</v>
+      </c>
+      <c r="O1" t="str">
+        <v>insurance_provider</v>
+      </c>
+      <c r="P1" t="str">
+        <v>insurance_policy_number</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>insurance_expiry</v>
+      </c>
+      <c r="R1" t="str">
         <v>notes</v>
       </c>
     </row>
@@ -617,19 +1487,359 @@
         <v>3</v>
       </c>
       <c r="J2" t="str">
+        <v>residential</v>
+      </c>
+      <c r="K2" t="str">
+        <v>active</v>
+      </c>
+      <c r="L2" t="str">
+        <v>today-1m</v>
+      </c>
+      <c r="M2">
+        <v>2700000</v>
+      </c>
+      <c r="N2">
+        <v>2800000</v>
+      </c>
+      <c r="O2" t="str">
+        <v>AXA Middle East</v>
+      </c>
+      <c r="P2" t="str">
+        <v>AXA-283876</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>today+11m</v>
+      </c>
+      <c r="R2" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R2"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K7"/>
+  <cols>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="17.83203125" customWidth="1"/>
+    <col min="9" max="9" width="19.83203125" customWidth="1"/>
+    <col min="10" max="10" width="14.83203125" customWidth="1"/>
+    <col min="11" max="11" width="14.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>tenant_phone</v>
+      </c>
+      <c r="B1" t="str">
+        <v>property_code</v>
+      </c>
+      <c r="C1" t="str">
+        <v>asset_name</v>
+      </c>
+      <c r="D1" t="str">
+        <v>kind</v>
+      </c>
+      <c r="E1" t="str">
+        <v>category</v>
+      </c>
+      <c r="F1" t="str">
+        <v>title</v>
+      </c>
+      <c r="G1" t="str">
+        <v>file_name</v>
+      </c>
+      <c r="H1" t="str">
+        <v>contract_number</v>
+      </c>
+      <c r="I1" t="str">
+        <v>work_order_number</v>
+      </c>
+      <c r="J1" t="str">
+        <v>issued_date</v>
+      </c>
+      <c r="K1" t="str">
+        <v>expiry_date</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>+961 76 725 502</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v>id</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v>National ID</v>
+      </c>
+      <c r="G2" t="str">
+        <v>rafic-salam-id.pdf</v>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
+      <c r="J2" t="str">
+        <v>today-7y</v>
+      </c>
+      <c r="K2" t="str">
+        <v>today+5y</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>+961 76 725 502</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v>contract</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v>Signed contract</v>
+      </c>
+      <c r="G3" t="str">
+        <v>CR-102-01.pdf</v>
+      </c>
+      <c r="H3" t="str">
+        <v>CR-102-01</v>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
+        <v>today+219d-12m</v>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v/>
+      </c>
+      <c r="B4" t="str">
+        <v>CR</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Elevator 1</v>
+      </c>
+      <c r="D4" t="str">
+        <v>other</v>
+      </c>
+      <c r="E4" t="str">
+        <v>certificate</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Elevator safety certificate</v>
+      </c>
+      <c r="G4" t="str">
+        <v>cr-elevator-1-certificate.pdf</v>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v>today-11m</v>
+      </c>
+      <c r="K4" t="str">
+        <v>today+6m</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v/>
+      </c>
+      <c r="B5" t="str">
+        <v>CR</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Fire alarm &amp; extinguishers</v>
+      </c>
+      <c r="D5" t="str">
+        <v>other</v>
+      </c>
+      <c r="E5" t="str">
+        <v>certificate</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Fire system compliance certificate</v>
+      </c>
+      <c r="G5" t="str">
+        <v>cr-fire-certificate.pdf</v>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v>today-10m</v>
+      </c>
+      <c r="K5" t="str">
+        <v>today+1m</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v/>
+      </c>
+      <c r="B6" t="str">
+        <v>CR</v>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6" t="str">
+        <v>other</v>
+      </c>
+      <c r="E6" t="str">
+        <v>insurance</v>
+      </c>
+      <c r="F6" t="str">
+        <v>AXA Middle East building policy</v>
+      </c>
+      <c r="G6" t="str">
+        <v>cr-insurance-policy.pdf</v>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
+        <v>today-8m</v>
+      </c>
+      <c r="K6" t="str">
+        <v>today+11m</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v/>
+      </c>
+      <c r="B7" t="str">
+        <v>CR</v>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v>other</v>
+      </c>
+      <c r="E7" t="str">
+        <v>ownership</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Title deed</v>
+      </c>
+      <c r="G7" t="str">
+        <v>cr-title-deed.pdf</v>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <v>today-1m</v>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:K7"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H1"/>
+  <cols>
+    <col min="1" max="1" width="17.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>contract_number</v>
+      </c>
+      <c r="B1" t="str">
+        <v>period</v>
+      </c>
+      <c r="C1" t="str">
+        <v>due_date</v>
+      </c>
+      <c r="D1" t="str">
+        <v>amount_due</v>
+      </c>
+      <c r="E1" t="str">
+        <v>amount_paid</v>
+      </c>
+      <c r="F1" t="str">
+        <v>paid_date</v>
+      </c>
+      <c r="G1" t="str">
+        <v>method</v>
+      </c>
+      <c r="H1" t="str">
+        <v>reference</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:M19"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -642,6 +1852,8 @@
     <col min="9" max="9" width="16.83203125" customWidth="1"/>
     <col min="10" max="10" width="14.83203125" customWidth="1"/>
     <col min="11" max="11" width="14.83203125" customWidth="1"/>
+    <col min="12" max="12" width="14.83203125" customWidth="1"/>
+    <col min="13" max="13" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -673,9 +1885,15 @@
         <v>asking_deposit</v>
       </c>
       <c r="J1" t="str">
+        <v>market_rent</v>
+      </c>
+      <c r="K1" t="str">
+        <v>condition</v>
+      </c>
+      <c r="L1" t="str">
         <v>status</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>notes</v>
       </c>
     </row>
@@ -696,7 +1914,7 @@
         <v>2</v>
       </c>
       <c r="F2">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="G2" t="str">
         <v>no</v>
@@ -707,10 +1925,16 @@
       <c r="I2">
         <v>1125</v>
       </c>
-      <c r="J2" t="str">
-        <v/>
+      <c r="J2">
+        <v>1200</v>
       </c>
       <c r="K2" t="str">
+        <v>good</v>
+      </c>
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
         <v/>
       </c>
     </row>
@@ -731,21 +1955,27 @@
         <v>1</v>
       </c>
       <c r="F3">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="G3" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="H3">
-        <v>975</v>
+        <v>900</v>
       </c>
       <c r="I3">
-        <v>975</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
+        <v>900</v>
+      </c>
+      <c r="J3">
+        <v>950</v>
       </c>
       <c r="K3" t="str">
+        <v>good</v>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
         <v/>
       </c>
     </row>
@@ -766,21 +1996,27 @@
         <v>1</v>
       </c>
       <c r="F4">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="G4" t="str">
         <v>yes</v>
       </c>
       <c r="H4">
-        <v>775</v>
+        <v>825</v>
       </c>
       <c r="I4">
-        <v>775</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
+        <v>825</v>
+      </c>
+      <c r="J4">
+        <v>850</v>
       </c>
       <c r="K4" t="str">
+        <v>good</v>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
         <v/>
       </c>
     </row>
@@ -801,21 +2037,27 @@
         <v>2</v>
       </c>
       <c r="F5">
-        <v>150</v>
+        <v>174</v>
       </c>
       <c r="G5" t="str">
         <v>no</v>
       </c>
       <c r="H5">
-        <v>1150</v>
+        <v>1125</v>
       </c>
       <c r="I5">
-        <v>1150</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
+        <v>1125</v>
+      </c>
+      <c r="J5">
+        <v>1225</v>
       </c>
       <c r="K5" t="str">
+        <v>good</v>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
         <v/>
       </c>
     </row>
@@ -836,21 +2078,27 @@
         <v>1</v>
       </c>
       <c r="F6">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G6" t="str">
-        <v>yes</v>
+        <v>no</v>
       </c>
       <c r="H6">
-        <v>1000</v>
+        <v>925</v>
       </c>
       <c r="I6">
-        <v>1000</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
+        <v>925</v>
+      </c>
+      <c r="J6">
+        <v>975</v>
       </c>
       <c r="K6" t="str">
+        <v>good</v>
+      </c>
+      <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
         <v/>
       </c>
     </row>
@@ -871,7 +2119,7 @@
         <v>1</v>
       </c>
       <c r="F7">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="G7" t="str">
         <v>no</v>
@@ -882,10 +2130,16 @@
       <c r="I7">
         <v>800</v>
       </c>
-      <c r="J7" t="str">
-        <v/>
+      <c r="J7">
+        <v>825</v>
       </c>
       <c r="K7" t="str">
+        <v>good</v>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
         <v/>
       </c>
     </row>
@@ -909,18 +2163,24 @@
         <v>179</v>
       </c>
       <c r="G8" t="str">
-        <v>yes</v>
+        <v>no</v>
       </c>
       <c r="H8">
-        <v>1175</v>
+        <v>1225</v>
       </c>
       <c r="I8">
-        <v>1175</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
+        <v>1225</v>
+      </c>
+      <c r="J8">
+        <v>1250</v>
       </c>
       <c r="K8" t="str">
+        <v>good</v>
+      </c>
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
         <v/>
       </c>
     </row>
@@ -941,7 +2201,7 @@
         <v>1</v>
       </c>
       <c r="F9">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G9" t="str">
         <v>no</v>
@@ -952,10 +2212,16 @@
       <c r="I9">
         <v>1025</v>
       </c>
-      <c r="J9" t="str">
-        <v/>
+      <c r="J9">
+        <v>1100</v>
       </c>
       <c r="K9" t="str">
+        <v>good</v>
+      </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
         <v/>
       </c>
     </row>
@@ -976,7 +2242,7 @@
         <v>1</v>
       </c>
       <c r="F10">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G10" t="str">
         <v>yes</v>
@@ -987,10 +2253,16 @@
       <c r="I10">
         <v>825</v>
       </c>
-      <c r="J10" t="str">
-        <v/>
+      <c r="J10">
+        <v>875</v>
       </c>
       <c r="K10" t="str">
+        <v>good</v>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
         <v/>
       </c>
     </row>
@@ -1011,21 +2283,27 @@
         <v>2</v>
       </c>
       <c r="F11">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="G11" t="str">
-        <v>yes</v>
+        <v>no</v>
       </c>
       <c r="H11">
+        <v>1200</v>
+      </c>
+      <c r="I11">
+        <v>1200</v>
+      </c>
+      <c r="J11">
         <v>1250</v>
       </c>
-      <c r="I11">
-        <v>1250</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
       <c r="K11" t="str">
+        <v>good</v>
+      </c>
+      <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
         <v/>
       </c>
     </row>
@@ -1046,21 +2324,27 @@
         <v>1</v>
       </c>
       <c r="F12">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G12" t="str">
         <v>no</v>
       </c>
       <c r="H12">
-        <v>1050</v>
+        <v>975</v>
       </c>
       <c r="I12">
-        <v>1050</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
+        <v>975</v>
+      </c>
+      <c r="J12">
+        <v>1000</v>
       </c>
       <c r="K12" t="str">
+        <v>fair</v>
+      </c>
+      <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
         <v/>
       </c>
     </row>
@@ -1081,21 +2365,27 @@
         <v>1</v>
       </c>
       <c r="F13">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="G13" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="H13">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="I13">
-        <v>900</v>
-      </c>
-      <c r="J13" t="str">
-        <v/>
+        <v>800</v>
+      </c>
+      <c r="J13">
+        <v>875</v>
       </c>
       <c r="K13" t="str">
+        <v>good</v>
+      </c>
+      <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
         <v/>
       </c>
     </row>
@@ -1116,7 +2406,7 @@
         <v>2</v>
       </c>
       <c r="F14">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="G14" t="str">
         <v>no</v>
@@ -1127,10 +2417,16 @@
       <c r="I14">
         <v>1150</v>
       </c>
-      <c r="J14" t="str">
-        <v/>
+      <c r="J14">
+        <v>1225</v>
       </c>
       <c r="K14" t="str">
+        <v>good</v>
+      </c>
+      <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
         <v/>
       </c>
     </row>
@@ -1151,21 +2447,27 @@
         <v>1</v>
       </c>
       <c r="F15">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="G15" t="str">
         <v>no</v>
       </c>
       <c r="H15">
-        <v>1050</v>
+        <v>1025</v>
       </c>
       <c r="I15">
-        <v>1050</v>
-      </c>
-      <c r="J15" t="str">
-        <v/>
+        <v>1025</v>
+      </c>
+      <c r="J15">
+        <v>1075</v>
       </c>
       <c r="K15" t="str">
+        <v>good</v>
+      </c>
+      <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
         <v/>
       </c>
     </row>
@@ -1186,21 +2488,27 @@
         <v>1</v>
       </c>
       <c r="F16">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G16" t="str">
         <v>no</v>
       </c>
       <c r="H16">
+        <v>825</v>
+      </c>
+      <c r="I16">
+        <v>825</v>
+      </c>
+      <c r="J16">
         <v>875</v>
       </c>
-      <c r="I16">
-        <v>875</v>
-      </c>
-      <c r="J16" t="str">
-        <v/>
-      </c>
       <c r="K16" t="str">
+        <v>good</v>
+      </c>
+      <c r="L16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str">
         <v/>
       </c>
     </row>
@@ -1221,21 +2529,27 @@
         <v>2</v>
       </c>
       <c r="F17">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="G17" t="str">
-        <v>yes</v>
+        <v>no</v>
       </c>
       <c r="H17">
+        <v>1225</v>
+      </c>
+      <c r="I17">
+        <v>1225</v>
+      </c>
+      <c r="J17">
         <v>1275</v>
       </c>
-      <c r="I17">
-        <v>1275</v>
-      </c>
-      <c r="J17" t="str">
-        <v/>
-      </c>
       <c r="K17" t="str">
+        <v>fair</v>
+      </c>
+      <c r="L17" t="str">
+        <v/>
+      </c>
+      <c r="M17" t="str">
         <v/>
       </c>
     </row>
@@ -1256,21 +2570,27 @@
         <v>1</v>
       </c>
       <c r="F18">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G18" t="str">
         <v>no</v>
       </c>
       <c r="H18">
-        <v>1000</v>
+        <v>1075</v>
       </c>
       <c r="I18">
-        <v>1000</v>
-      </c>
-      <c r="J18" t="str">
-        <v/>
+        <v>1075</v>
+      </c>
+      <c r="J18">
+        <v>1100</v>
       </c>
       <c r="K18" t="str">
+        <v>good</v>
+      </c>
+      <c r="L18" t="str">
+        <v/>
+      </c>
+      <c r="M18" t="str">
         <v/>
       </c>
     </row>
@@ -1291,27 +2611,33 @@
         <v>1</v>
       </c>
       <c r="F19">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="G19" t="str">
         <v>no</v>
       </c>
       <c r="H19">
-        <v>850</v>
+        <v>900</v>
       </c>
       <c r="I19">
-        <v>850</v>
-      </c>
-      <c r="J19" t="str">
-        <v/>
+        <v>900</v>
+      </c>
+      <c r="J19">
+        <v>925</v>
       </c>
       <c r="K19" t="str">
+        <v>good</v>
+      </c>
+      <c r="L19" t="str">
+        <v/>
+      </c>
+      <c r="M19" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M19"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1370,16 +2696,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Jad</v>
+        <v>Naji</v>
       </c>
       <c r="B2" t="str">
-        <v>Dagher</v>
+        <v>Assaf</v>
       </c>
       <c r="C2" t="str">
-        <v>+961 70 489 845</v>
+        <v>+961 70 273 489</v>
       </c>
       <c r="D2" t="str">
-        <v>jad.dagher@example.com</v>
+        <v>naji.assaf@example.com</v>
       </c>
       <c r="E2" t="str">
         <v>Lebanese</v>
@@ -1388,16 +2714,16 @@
         <v>national_id</v>
       </c>
       <c r="G2" t="str">
-        <v>LB-6900604</v>
+        <v>LB-7336817</v>
       </c>
       <c r="H2" t="str">
         <v>Designer</v>
       </c>
       <c r="I2" t="str">
-        <v/>
+        <v>Naji Assaf</v>
       </c>
       <c r="J2" t="str">
-        <v>+961 71 534 988</v>
+        <v>+961 70 132 763</v>
       </c>
       <c r="K2" t="str">
         <v/>
@@ -1405,16 +2731,16 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Rima</v>
+        <v>Rafic</v>
       </c>
       <c r="B3" t="str">
-        <v>Fares</v>
+        <v>Chahine</v>
       </c>
       <c r="C3" t="str">
-        <v>+961 78 642 109</v>
+        <v>+961 76 677 875</v>
       </c>
       <c r="D3" t="str">
-        <v>rima.fares@example.com</v>
+        <v>rafic.chahine@example.com</v>
       </c>
       <c r="E3" t="str">
         <v>Lebanese</v>
@@ -1423,16 +2749,16 @@
         <v>national_id</v>
       </c>
       <c r="G3" t="str">
-        <v>LB-1685442</v>
+        <v>LB-1926075</v>
       </c>
       <c r="H3" t="str">
-        <v>Bank officer</v>
+        <v>Teacher</v>
       </c>
       <c r="I3" t="str">
-        <v/>
+        <v>Sara Chahine</v>
       </c>
       <c r="J3" t="str">
-        <v>+961 79 751 636</v>
+        <v/>
       </c>
       <c r="K3" t="str">
         <v/>
@@ -1440,16 +2766,16 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Antoine</v>
+        <v>Maria</v>
       </c>
       <c r="B4" t="str">
-        <v>Baydoun</v>
+        <v>Kanaan</v>
       </c>
       <c r="C4" t="str">
-        <v>+961 70 108 759</v>
+        <v>+961 81 756 543</v>
       </c>
       <c r="D4" t="str">
-        <v>antoine.baydoun@example.com</v>
+        <v>maria.kanaan@example.com</v>
       </c>
       <c r="E4" t="str">
         <v>Lebanese</v>
@@ -1458,16 +2784,16 @@
         <v>national_id</v>
       </c>
       <c r="G4" t="str">
-        <v>LB-7737871</v>
+        <v>LB-9046313</v>
       </c>
       <c r="H4" t="str">
-        <v>Journalist</v>
+        <v>Lawyer</v>
       </c>
       <c r="I4" t="str">
-        <v/>
+        <v>Josiane Kanaan</v>
       </c>
       <c r="J4" t="str">
-        <v>+961 76 953 284</v>
+        <v/>
       </c>
       <c r="K4" t="str">
         <v/>
@@ -1475,16 +2801,16 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Antoine</v>
+        <v>Michel</v>
       </c>
       <c r="B5" t="str">
-        <v>Nasrallah</v>
+        <v>Issa</v>
       </c>
       <c r="C5" t="str">
-        <v>+961 78 258 933</v>
+        <v>+961 76 748 409</v>
       </c>
       <c r="D5" t="str">
-        <v>antoine.nasrallah@example.com</v>
+        <v>michel.issa@example.com</v>
       </c>
       <c r="E5" t="str">
         <v>Lebanese</v>
@@ -1493,16 +2819,16 @@
         <v>national_id</v>
       </c>
       <c r="G5" t="str">
-        <v>LB-4126818</v>
+        <v>LB-6422706</v>
       </c>
       <c r="H5" t="str">
-        <v>Bank officer</v>
+        <v>Software developer</v>
       </c>
       <c r="I5" t="str">
-        <v>Nada Nasrallah</v>
+        <v>Rola Issa</v>
       </c>
       <c r="J5" t="str">
-        <v>+961 79 386 582</v>
+        <v/>
       </c>
       <c r="K5" t="str">
         <v/>
@@ -1510,34 +2836,34 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Rony</v>
+        <v>Salim</v>
       </c>
       <c r="B6" t="str">
-        <v>Hajj</v>
+        <v>Nasrallah</v>
       </c>
       <c r="C6" t="str">
-        <v>+961 81 751 494</v>
+        <v>+961 3 203 636</v>
       </c>
       <c r="D6" t="str">
-        <v>rony.hajj@example.com</v>
+        <v>salim.nasrallah@example.com</v>
       </c>
       <c r="E6" t="str">
-        <v>Jordanian</v>
+        <v>Lebanese</v>
       </c>
       <c r="F6" t="str">
         <v>passport</v>
       </c>
       <c r="G6" t="str">
-        <v>RL4787623</v>
+        <v>RL6994790</v>
       </c>
       <c r="H6" t="str">
-        <v>Bank officer</v>
+        <v>Teacher</v>
       </c>
       <c r="I6" t="str">
-        <v/>
+        <v>Walid Nasrallah</v>
       </c>
       <c r="J6" t="str">
-        <v>+961 76 784 663</v>
+        <v>+961 70 204 524</v>
       </c>
       <c r="K6" t="str">
         <v/>
@@ -1545,31 +2871,31 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Maya</v>
+        <v>Reem</v>
       </c>
       <c r="B7" t="str">
-        <v>Rizk</v>
+        <v>Hobeika</v>
       </c>
       <c r="C7" t="str">
-        <v>+961 79 533 713</v>
+        <v>+961 81 657 709</v>
       </c>
       <c r="D7" t="str">
-        <v>maya.rizk@example.com</v>
+        <v>reem.hobeika@example.com</v>
       </c>
       <c r="E7" t="str">
-        <v>Egyptian</v>
+        <v>Lebanese</v>
       </c>
       <c r="F7" t="str">
         <v>passport</v>
       </c>
       <c r="G7" t="str">
-        <v>RL6775325</v>
+        <v>RL7630636</v>
       </c>
       <c r="H7" t="str">
-        <v>Accountant</v>
+        <v>Architect</v>
       </c>
       <c r="I7" t="str">
-        <v>Khaled Rizk</v>
+        <v/>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -1580,34 +2906,34 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Roy</v>
+        <v>Rafic</v>
       </c>
       <c r="B8" t="str">
-        <v>Fakhoury</v>
+        <v>Salam</v>
       </c>
       <c r="C8" t="str">
-        <v>+961 71 801 321</v>
+        <v>+961 76 725 502</v>
       </c>
       <c r="D8" t="str">
-        <v>roy.fakhoury@example.com</v>
+        <v>rafic.salam@example.com</v>
       </c>
       <c r="E8" t="str">
         <v>Lebanese</v>
       </c>
       <c r="F8" t="str">
-        <v>passport</v>
+        <v>national_id</v>
       </c>
       <c r="G8" t="str">
-        <v>RL4085610</v>
+        <v>LB-7246100</v>
       </c>
       <c r="H8" t="str">
-        <v>Designer</v>
+        <v>Accountant</v>
       </c>
       <c r="I8" t="str">
-        <v>Marie Fakhoury</v>
+        <v>Mirna Salam</v>
       </c>
       <c r="J8" t="str">
-        <v>+961 70 164 924</v>
+        <v>+961 79 254 849</v>
       </c>
       <c r="K8" t="str">
         <v/>
@@ -1615,28 +2941,28 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Ali</v>
+        <v>Habib</v>
       </c>
       <c r="B9" t="str">
-        <v>Nassar</v>
+        <v>Sfeir</v>
       </c>
       <c r="C9" t="str">
-        <v>+961 78 828 106</v>
+        <v>+961 70 375 586</v>
       </c>
       <c r="D9" t="str">
-        <v>ali.nassar@example.com</v>
+        <v>habib.sfeir@example.com</v>
       </c>
       <c r="E9" t="str">
-        <v>Canadian</v>
+        <v>Lebanese</v>
       </c>
       <c r="F9" t="str">
-        <v>passport</v>
+        <v>national_id</v>
       </c>
       <c r="G9" t="str">
-        <v>RL7106746</v>
+        <v>LB-5689249</v>
       </c>
       <c r="H9" t="str">
-        <v>Consultant</v>
+        <v>Restaurant owner</v>
       </c>
       <c r="I9" t="str">
         <v/>
@@ -1650,34 +2976,34 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Sandra</v>
+        <v>Jana</v>
       </c>
       <c r="B10" t="str">
-        <v>Baydoun</v>
+        <v>Sfeir</v>
       </c>
       <c r="C10" t="str">
-        <v>+961 79 438 693</v>
+        <v>+961 71 227 191</v>
       </c>
       <c r="D10" t="str">
-        <v>sandra.baydoun@example.com</v>
+        <v>jana.sfeir@example.com</v>
       </c>
       <c r="E10" t="str">
         <v>Lebanese</v>
       </c>
       <c r="F10" t="str">
-        <v>national_id</v>
+        <v>passport</v>
       </c>
       <c r="G10" t="str">
-        <v>LB-6019906</v>
+        <v>RL4727899</v>
       </c>
       <c r="H10" t="str">
-        <v>Architect</v>
+        <v>Teacher</v>
       </c>
       <c r="I10" t="str">
-        <v>Kamal Baydoun</v>
+        <v>Rana Sfeir</v>
       </c>
       <c r="J10" t="str">
-        <v>+961 70 550 287</v>
+        <v>+961 78 418 888</v>
       </c>
       <c r="K10" t="str">
         <v/>
@@ -1685,34 +3011,34 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Imad</v>
+        <v>Youssef</v>
       </c>
       <c r="B11" t="str">
-        <v>Maalouf</v>
+        <v>Osseiran</v>
       </c>
       <c r="C11" t="str">
-        <v>+961 78 872 553</v>
+        <v>+961 71 565 882</v>
       </c>
       <c r="D11" t="str">
-        <v>imad.maalouf@example.com</v>
+        <v>youssef.osseiran@example.com</v>
       </c>
       <c r="E11" t="str">
-        <v>Lebanese</v>
+        <v>Canadian</v>
       </c>
       <c r="F11" t="str">
-        <v>national_id</v>
+        <v>passport</v>
       </c>
       <c r="G11" t="str">
-        <v>LB-8511653</v>
+        <v>RL6429763</v>
       </c>
       <c r="H11" t="str">
-        <v>Teacher</v>
+        <v>Lawyer</v>
       </c>
       <c r="I11" t="str">
-        <v>Sara Maalouf</v>
+        <v/>
       </c>
       <c r="J11" t="str">
-        <v/>
+        <v>+961 76 363 346</v>
       </c>
       <c r="K11" t="str">
         <v/>
@@ -1720,34 +3046,34 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Walid</v>
+        <v>Ibrahim</v>
       </c>
       <c r="B12" t="str">
-        <v>Ayoub</v>
+        <v>Hanna</v>
       </c>
       <c r="C12" t="str">
-        <v>+961 70 701 949</v>
+        <v>+961 3 686 354</v>
       </c>
       <c r="D12" t="str">
-        <v>walid.ayoub@example.com</v>
+        <v>ibrahim.hanna@example.com</v>
       </c>
       <c r="E12" t="str">
-        <v>Syrian</v>
+        <v>French</v>
       </c>
       <c r="F12" t="str">
         <v>passport</v>
       </c>
       <c r="G12" t="str">
-        <v>RL1245733</v>
+        <v>RL6087612</v>
       </c>
       <c r="H12" t="str">
-        <v>Nurse</v>
+        <v>Accountant</v>
       </c>
       <c r="I12" t="str">
-        <v>Rita Ayoub</v>
+        <v/>
       </c>
       <c r="J12" t="str">
-        <v>+961 78 647 728</v>
+        <v>+961 81 520 175</v>
       </c>
       <c r="K12" t="str">
         <v/>
@@ -1755,16 +3081,16 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Tarek</v>
+        <v>Walid</v>
       </c>
       <c r="B13" t="str">
-        <v>Kfoury</v>
+        <v>Hajj</v>
       </c>
       <c r="C13" t="str">
-        <v>+961 81 524 789</v>
+        <v>+961 70 335 953</v>
       </c>
       <c r="D13" t="str">
-        <v>tarek.kfoury@example.com</v>
+        <v>walid.hajj@example.com</v>
       </c>
       <c r="E13" t="str">
         <v>Lebanese</v>
@@ -1773,16 +3099,16 @@
         <v>passport</v>
       </c>
       <c r="G13" t="str">
-        <v>RL5683314</v>
+        <v>RL9566406</v>
       </c>
       <c r="H13" t="str">
-        <v>Bank officer</v>
+        <v>Software developer</v>
       </c>
       <c r="I13" t="str">
-        <v>Pascale Kfoury</v>
+        <v>Lamia Hajj</v>
       </c>
       <c r="J13" t="str">
-        <v>+961 70 267 964</v>
+        <v>+961 3 972 945</v>
       </c>
       <c r="K13" t="str">
         <v/>
@@ -1790,34 +3116,34 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Tala</v>
+        <v>Sami</v>
       </c>
       <c r="B14" t="str">
-        <v>Chehab</v>
+        <v>Frem</v>
       </c>
       <c r="C14" t="str">
-        <v>+961 70 969 500</v>
+        <v>+961 81 905 824</v>
       </c>
       <c r="D14" t="str">
-        <v>tala.chehab@example.com</v>
+        <v>sami.frem@example.com</v>
       </c>
       <c r="E14" t="str">
         <v>Lebanese</v>
       </c>
       <c r="F14" t="str">
-        <v>passport</v>
+        <v>national_id</v>
       </c>
       <c r="G14" t="str">
-        <v>RL5435856</v>
+        <v>LB-5879694</v>
       </c>
       <c r="H14" t="str">
-        <v>Lawyer</v>
+        <v>Pharmacist</v>
       </c>
       <c r="I14" t="str">
-        <v>Pascale Chehab</v>
+        <v>Samir Frem</v>
       </c>
       <c r="J14" t="str">
-        <v/>
+        <v>+961 76 407 322</v>
       </c>
       <c r="K14" t="str">
         <v/>
@@ -1825,16 +3151,16 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Selim</v>
+        <v>Tarek</v>
       </c>
       <c r="B15" t="str">
-        <v>Kassab</v>
+        <v>Sinno</v>
       </c>
       <c r="C15" t="str">
-        <v>+961 3 800 428</v>
+        <v>+961 3 537 292</v>
       </c>
       <c r="D15" t="str">
-        <v>selim.kassab@example.com</v>
+        <v>tarek.sinno@example.com</v>
       </c>
       <c r="E15" t="str">
         <v>Lebanese</v>
@@ -1843,16 +3169,16 @@
         <v>national_id</v>
       </c>
       <c r="G15" t="str">
-        <v>LB-4604729</v>
+        <v/>
       </c>
       <c r="H15" t="str">
-        <v>Physician</v>
+        <v>Dentist</v>
       </c>
       <c r="I15" t="str">
-        <v>Fadi Kassab</v>
+        <v>Bassam Sinno</v>
       </c>
       <c r="J15" t="str">
-        <v/>
+        <v>+961 70 102 924</v>
       </c>
       <c r="K15" t="str">
         <v/>
@@ -1867,7 +3193,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:T15"/>
   <cols>
     <col min="1" max="1" width="17.83203125" customWidth="1"/>
     <col min="2" max="2" width="15.83203125" customWidth="1"/>
@@ -1878,11 +3204,17 @@
     <col min="7" max="7" width="14.83203125" customWidth="1"/>
     <col min="8" max="8" width="14.83203125" customWidth="1"/>
     <col min="9" max="9" width="14.83203125" customWidth="1"/>
-    <col min="10" max="10" width="16.83203125" customWidth="1"/>
-    <col min="11" max="11" width="14.83203125" customWidth="1"/>
-    <col min="12" max="12" width="15.83203125" customWidth="1"/>
-    <col min="13" max="13" width="14.83203125" customWidth="1"/>
-    <col min="14" max="14" width="17.83203125" customWidth="1"/>
+    <col min="10" max="10" width="19.83203125" customWidth="1"/>
+    <col min="11" max="11" width="16.83203125" customWidth="1"/>
+    <col min="12" max="12" width="14.83203125" customWidth="1"/>
+    <col min="13" max="13" width="15.83203125" customWidth="1"/>
+    <col min="14" max="14" width="22.83203125" customWidth="1"/>
+    <col min="15" max="15" width="15.83203125" customWidth="1"/>
+    <col min="16" max="16" width="18.83203125" customWidth="1"/>
+    <col min="17" max="17" width="15.83203125" customWidth="1"/>
+    <col min="18" max="18" width="15.83203125" customWidth="1"/>
+    <col min="19" max="19" width="14.83203125" customWidth="1"/>
+    <col min="20" max="20" width="17.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1914,54 +3246,72 @@
         <v>payment_day</v>
       </c>
       <c r="J1" t="str">
+        <v>payment_frequency</v>
+      </c>
+      <c r="K1" t="str">
         <v>payment_method</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>status</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>move_out_date</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
+        <v>rent_increase_clause</v>
+      </c>
+      <c r="O1" t="str">
+        <v>special_terms</v>
+      </c>
+      <c r="P1" t="str">
+        <v>renewal_decision</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>proposed_rent</v>
+      </c>
+      <c r="R1" t="str">
+        <v>renewal_notes</v>
+      </c>
+      <c r="S1" t="str">
         <v>notes</v>
       </c>
-      <c r="N1" t="str">
+      <c r="T1" t="str">
         <v>payment_pattern</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>CR-203-01</v>
+        <v>CR-101-01</v>
       </c>
       <c r="B2" t="str">
         <v>CR</v>
       </c>
       <c r="C2" t="str">
-        <v>203</v>
+        <v>101</v>
       </c>
       <c r="D2" t="str">
-        <v>+961 70 489 845</v>
+        <v>+961 70 273 489</v>
       </c>
       <c r="E2" t="str">
-        <v>today+98d-24m</v>
+        <v>today+236d-12m</v>
       </c>
       <c r="F2" t="str">
-        <v>today+98d</v>
+        <v>today+236d</v>
       </c>
       <c r="G2">
-        <v>800</v>
+        <v>1125</v>
       </c>
       <c r="H2">
-        <v>800</v>
+        <v>1125</v>
       </c>
       <c r="I2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J2" t="str">
-        <v>bank_transfer</v>
+        <v>monthly</v>
       </c>
       <c r="K2" t="str">
-        <v/>
+        <v>cheque</v>
       </c>
       <c r="L2" t="str">
         <v/>
@@ -1970,42 +3320,60 @@
         <v/>
       </c>
       <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
+        <v/>
+      </c>
+      <c r="S2" t="str">
+        <v/>
+      </c>
+      <c r="T2" t="str">
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>CR-103-01</v>
+        <v>CR-201-01</v>
       </c>
       <c r="B3" t="str">
         <v>CR</v>
       </c>
       <c r="C3" t="str">
-        <v>103</v>
+        <v>201</v>
       </c>
       <c r="D3" t="str">
-        <v>+961 78 642 109</v>
+        <v>+961 76 677 875</v>
       </c>
       <c r="E3" t="str">
-        <v>today+130d-24m</v>
+        <v>today+75d-24m</v>
       </c>
       <c r="F3" t="str">
-        <v>today+130d</v>
+        <v>today+75d</v>
       </c>
       <c r="G3">
-        <v>775</v>
+        <v>1125</v>
       </c>
       <c r="H3">
-        <v>775</v>
+        <v>1125</v>
       </c>
       <c r="I3">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J3" t="str">
-        <v>cheque</v>
+        <v>monthly</v>
       </c>
       <c r="K3" t="str">
-        <v/>
+        <v>cash</v>
       </c>
       <c r="L3" t="str">
         <v/>
@@ -2014,43 +3382,61 @@
         <v/>
       </c>
       <c r="N3" t="str">
+        <v>CPI-linked on renewal</v>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
+      <c r="R3" t="str">
+        <v/>
+      </c>
+      <c r="S3" t="str">
+        <v/>
+      </c>
+      <c r="T3" t="str">
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>CR-202-01</v>
+        <v>CR-301-01</v>
       </c>
       <c r="B4" t="str">
         <v>CR</v>
       </c>
       <c r="C4" t="str">
-        <v>202</v>
+        <v>301</v>
       </c>
       <c r="D4" t="str">
-        <v>+961 70 108 759</v>
+        <v>+961 81 756 543</v>
       </c>
       <c r="E4" t="str">
-        <v>today+181d-24m</v>
+        <v>today+198d-24m</v>
       </c>
       <c r="F4" t="str">
-        <v>today+181d</v>
+        <v>today+198d</v>
       </c>
       <c r="G4">
-        <v>1000</v>
+        <v>1225</v>
       </c>
       <c r="H4">
-        <v>1000</v>
+        <v>1225</v>
       </c>
       <c r="I4">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="J4" t="str">
+        <v>monthly</v>
+      </c>
+      <c r="K4" t="str">
         <v>bank_transfer</v>
       </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
       <c r="L4" t="str">
         <v/>
       </c>
@@ -2058,42 +3444,60 @@
         <v/>
       </c>
       <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
+        <v/>
+      </c>
+      <c r="R4" t="str">
+        <v/>
+      </c>
+      <c r="S4" t="str">
+        <v/>
+      </c>
+      <c r="T4" t="str">
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>CR-101-01</v>
+        <v>CR-401-01</v>
       </c>
       <c r="B5" t="str">
         <v>CR</v>
       </c>
       <c r="C5" t="str">
-        <v>101</v>
+        <v>401</v>
       </c>
       <c r="D5" t="str">
-        <v>+961 78 258 933</v>
+        <v>+961 76 748 409</v>
       </c>
       <c r="E5" t="str">
-        <v>today+258d-12m</v>
+        <v>today+319d-12m</v>
       </c>
       <c r="F5" t="str">
-        <v>today+258d</v>
+        <v>today+319d</v>
       </c>
       <c r="G5">
-        <v>1125</v>
+        <v>1200</v>
       </c>
       <c r="H5">
-        <v>1125</v>
+        <v>1200</v>
       </c>
       <c r="I5">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J5" t="str">
-        <v>cash</v>
+        <v>monthly</v>
       </c>
       <c r="K5" t="str">
-        <v/>
+        <v>bank_transfer</v>
       </c>
       <c r="L5" t="str">
         <v/>
@@ -2102,42 +3506,60 @@
         <v/>
       </c>
       <c r="N5" t="str">
+        <v>5% on renewal</v>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+      <c r="Q5" t="str">
+        <v/>
+      </c>
+      <c r="R5" t="str">
+        <v/>
+      </c>
+      <c r="S5" t="str">
+        <v/>
+      </c>
+      <c r="T5" t="str">
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>CR-102-01</v>
+        <v>CR-202-01</v>
       </c>
       <c r="B6" t="str">
         <v>CR</v>
       </c>
       <c r="C6" t="str">
-        <v>102</v>
+        <v>202</v>
       </c>
       <c r="D6" t="str">
-        <v>+961 81 751 494</v>
+        <v>+961 3 203 636</v>
       </c>
       <c r="E6" t="str">
-        <v>today+268d-24m</v>
+        <v>today+136d-12m</v>
       </c>
       <c r="F6" t="str">
-        <v>today+268d</v>
+        <v>today+136d</v>
       </c>
       <c r="G6">
-        <v>975</v>
+        <v>925</v>
       </c>
       <c r="H6">
-        <v>975</v>
+        <v>925</v>
       </c>
       <c r="I6">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J6" t="str">
-        <v>bank_transfer</v>
+        <v>monthly</v>
       </c>
       <c r="K6" t="str">
-        <v/>
+        <v>cheque</v>
       </c>
       <c r="L6" t="str">
         <v/>
@@ -2146,43 +3568,61 @@
         <v/>
       </c>
       <c r="N6" t="str">
+        <v>5% on renewal</v>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <v/>
+      </c>
+      <c r="Q6" t="str">
+        <v/>
+      </c>
+      <c r="R6" t="str">
+        <v/>
+      </c>
+      <c r="S6" t="str">
+        <v/>
+      </c>
+      <c r="T6" t="str">
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>CR-302-01</v>
+        <v>CR-303-01</v>
       </c>
       <c r="B7" t="str">
         <v>CR</v>
       </c>
       <c r="C7" t="str">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D7" t="str">
-        <v>+961 79 533 713</v>
+        <v>+961 81 657 709</v>
       </c>
       <c r="E7" t="str">
-        <v>today+162d-12m</v>
+        <v>today+201d-12m</v>
       </c>
       <c r="F7" t="str">
-        <v>today+162d</v>
+        <v>today+201d</v>
       </c>
       <c r="G7">
-        <v>1025</v>
+        <v>825</v>
       </c>
       <c r="H7">
-        <v>1025</v>
+        <v>825</v>
       </c>
       <c r="I7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J7" t="str">
+        <v>monthly</v>
+      </c>
+      <c r="K7" t="str">
         <v>cheque</v>
       </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
       <c r="L7" t="str">
         <v/>
       </c>
@@ -2190,42 +3630,60 @@
         <v/>
       </c>
       <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v/>
+      </c>
+      <c r="Q7" t="str">
+        <v/>
+      </c>
+      <c r="R7" t="str">
+        <v/>
+      </c>
+      <c r="S7" t="str">
+        <v/>
+      </c>
+      <c r="T7" t="str">
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>CR-503-01</v>
+        <v>CR-102-01</v>
       </c>
       <c r="B8" t="str">
         <v>CR</v>
       </c>
       <c r="C8" t="str">
-        <v>503</v>
+        <v>102</v>
       </c>
       <c r="D8" t="str">
-        <v>+961 71 801 321</v>
+        <v>+961 76 725 502</v>
       </c>
       <c r="E8" t="str">
-        <v>today+189d-12m</v>
+        <v>today+219d-12m</v>
       </c>
       <c r="F8" t="str">
-        <v>today+189d</v>
+        <v>today+219d</v>
       </c>
       <c r="G8">
-        <v>875</v>
+        <v>900</v>
       </c>
       <c r="H8">
-        <v>875</v>
+        <v>900</v>
       </c>
       <c r="I8">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="J8" t="str">
-        <v>cash</v>
+        <v>monthly</v>
       </c>
       <c r="K8" t="str">
-        <v/>
+        <v>bank_transfer</v>
       </c>
       <c r="L8" t="str">
         <v/>
@@ -2234,42 +3692,60 @@
         <v/>
       </c>
       <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+      <c r="Q8" t="str">
+        <v/>
+      </c>
+      <c r="R8" t="str">
+        <v/>
+      </c>
+      <c r="S8" t="str">
+        <v/>
+      </c>
+      <c r="T8" t="str">
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>CR-603-01</v>
+        <v>CR-103-01</v>
       </c>
       <c r="B9" t="str">
         <v>CR</v>
       </c>
       <c r="C9" t="str">
-        <v>603</v>
+        <v>103</v>
       </c>
       <c r="D9" t="str">
-        <v>+961 78 828 106</v>
+        <v>+961 70 375 586</v>
       </c>
       <c r="E9" t="str">
-        <v>today+197d-24m</v>
+        <v>today+82d-12m</v>
       </c>
       <c r="F9" t="str">
-        <v>today+197d</v>
+        <v>today+82d</v>
       </c>
       <c r="G9">
-        <v>850</v>
+        <v>825</v>
       </c>
       <c r="H9">
-        <v>850</v>
+        <v>825</v>
       </c>
       <c r="I9">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J9" t="str">
-        <v>bank_transfer</v>
+        <v>monthly</v>
       </c>
       <c r="K9" t="str">
-        <v/>
+        <v>cheque</v>
       </c>
       <c r="L9" t="str">
         <v/>
@@ -2278,43 +3754,61 @@
         <v/>
       </c>
       <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+      <c r="Q9" t="str">
+        <v/>
+      </c>
+      <c r="R9" t="str">
+        <v/>
+      </c>
+      <c r="S9" t="str">
+        <v/>
+      </c>
+      <c r="T9" t="str">
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>CR-401-01</v>
+        <v>CR-302-01</v>
       </c>
       <c r="B10" t="str">
         <v>CR</v>
       </c>
       <c r="C10" t="str">
-        <v>401</v>
+        <v>302</v>
       </c>
       <c r="D10" t="str">
-        <v>+961 79 438 693</v>
+        <v>+961 71 227 191</v>
       </c>
       <c r="E10" t="str">
-        <v>today+317d-12m</v>
+        <v>today+105d-24m</v>
       </c>
       <c r="F10" t="str">
-        <v>today+317d</v>
+        <v>today+105d</v>
       </c>
       <c r="G10">
-        <v>1250</v>
+        <v>1025</v>
       </c>
       <c r="H10">
-        <v>1250</v>
+        <v>1025</v>
       </c>
       <c r="I10">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J10" t="str">
+        <v>monthly</v>
+      </c>
+      <c r="K10" t="str">
         <v>cheque</v>
       </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
       <c r="L10" t="str">
         <v/>
       </c>
@@ -2322,42 +3816,60 @@
         <v/>
       </c>
       <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10" t="str">
+        <v/>
+      </c>
+      <c r="Q10" t="str">
+        <v/>
+      </c>
+      <c r="R10" t="str">
+        <v/>
+      </c>
+      <c r="S10" t="str">
+        <v/>
+      </c>
+      <c r="T10" t="str">
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>CR-402-01</v>
+        <v>CR-601-01</v>
       </c>
       <c r="B11" t="str">
         <v>CR</v>
       </c>
       <c r="C11" t="str">
-        <v>402</v>
+        <v>601</v>
       </c>
       <c r="D11" t="str">
-        <v>+961 78 872 553</v>
+        <v>+961 71 565 882</v>
       </c>
       <c r="E11" t="str">
-        <v>today+141d-12m</v>
+        <v>today+218d-24m</v>
       </c>
       <c r="F11" t="str">
-        <v>today+141d</v>
+        <v>today+218d</v>
       </c>
       <c r="G11">
-        <v>1050</v>
+        <v>1225</v>
       </c>
       <c r="H11">
-        <v>1050</v>
+        <v>1225</v>
       </c>
       <c r="I11">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="J11" t="str">
-        <v>bank_transfer</v>
+        <v>monthly</v>
       </c>
       <c r="K11" t="str">
-        <v/>
+        <v>cheque</v>
       </c>
       <c r="L11" t="str">
         <v/>
@@ -2366,43 +3878,61 @@
         <v/>
       </c>
       <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
+        <v/>
+      </c>
+      <c r="Q11" t="str">
+        <v/>
+      </c>
+      <c r="R11" t="str">
+        <v/>
+      </c>
+      <c r="S11" t="str">
+        <v/>
+      </c>
+      <c r="T11" t="str">
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>CR-502-01</v>
+        <v>CR-402-01</v>
       </c>
       <c r="B12" t="str">
         <v>CR</v>
       </c>
       <c r="C12" t="str">
-        <v>502</v>
+        <v>402</v>
       </c>
       <c r="D12" t="str">
-        <v>+961 70 701 949</v>
+        <v>+961 3 686 354</v>
       </c>
       <c r="E12" t="str">
-        <v>today+188d-12m</v>
+        <v>today+118d-12m</v>
       </c>
       <c r="F12" t="str">
-        <v>today+188d</v>
+        <v>today+118d</v>
       </c>
       <c r="G12">
-        <v>1050</v>
+        <v>975</v>
       </c>
       <c r="H12">
-        <v>1050</v>
+        <v>975</v>
       </c>
       <c r="I12">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J12" t="str">
+        <v>monthly</v>
+      </c>
+      <c r="K12" t="str">
         <v>bank_transfer</v>
       </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
       <c r="L12" t="str">
         <v/>
       </c>
@@ -2410,43 +3940,61 @@
         <v/>
       </c>
       <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v/>
+      </c>
+      <c r="P12" t="str">
+        <v/>
+      </c>
+      <c r="Q12" t="str">
+        <v/>
+      </c>
+      <c r="R12" t="str">
+        <v/>
+      </c>
+      <c r="S12" t="str">
+        <v/>
+      </c>
+      <c r="T12" t="str">
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>CR-403-01</v>
+        <v>CR-501-01</v>
       </c>
       <c r="B13" t="str">
         <v>CR</v>
       </c>
       <c r="C13" t="str">
-        <v>403</v>
+        <v>501</v>
       </c>
       <c r="D13" t="str">
-        <v>+961 81 524 789</v>
+        <v>+961 70 335 953</v>
       </c>
       <c r="E13" t="str">
-        <v>today+99d-24m</v>
+        <v>today+254d-12m</v>
       </c>
       <c r="F13" t="str">
-        <v>today+99d</v>
+        <v>today+254d</v>
       </c>
       <c r="G13">
-        <v>900</v>
+        <v>1150</v>
       </c>
       <c r="H13">
-        <v>900</v>
+        <v>1150</v>
       </c>
       <c r="I13">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J13" t="str">
+        <v>monthly</v>
+      </c>
+      <c r="K13" t="str">
         <v>cash</v>
       </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
       <c r="L13" t="str">
         <v/>
       </c>
@@ -2454,43 +4002,61 @@
         <v/>
       </c>
       <c r="N13" t="str">
+        <v>CPI-linked on renewal</v>
+      </c>
+      <c r="O13" t="str">
+        <v/>
+      </c>
+      <c r="P13" t="str">
+        <v/>
+      </c>
+      <c r="Q13" t="str">
+        <v/>
+      </c>
+      <c r="R13" t="str">
+        <v/>
+      </c>
+      <c r="S13" t="str">
+        <v/>
+      </c>
+      <c r="T13" t="str">
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>CR-303-01</v>
+        <v>CR-502-01</v>
       </c>
       <c r="B14" t="str">
         <v>CR</v>
       </c>
       <c r="C14" t="str">
-        <v>303</v>
+        <v>502</v>
       </c>
       <c r="D14" t="str">
-        <v>+961 70 969 500</v>
+        <v>+961 81 905 824</v>
       </c>
       <c r="E14" t="str">
-        <v>today+208d-12m</v>
+        <v>today+81d-12m</v>
       </c>
       <c r="F14" t="str">
-        <v>today+208d</v>
+        <v>today+81d</v>
       </c>
       <c r="G14">
-        <v>825</v>
+        <v>1025</v>
       </c>
       <c r="H14">
-        <v>825</v>
+        <v>1025</v>
       </c>
       <c r="I14">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="J14" t="str">
+        <v>monthly</v>
+      </c>
+      <c r="K14" t="str">
         <v>bank_transfer</v>
       </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
       <c r="L14" t="str">
         <v/>
       </c>
@@ -2498,6 +4064,24 @@
         <v/>
       </c>
       <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v/>
+      </c>
+      <c r="P14" t="str">
+        <v/>
+      </c>
+      <c r="Q14" t="str">
+        <v/>
+      </c>
+      <c r="R14" t="str">
+        <v/>
+      </c>
+      <c r="S14" t="str">
+        <v/>
+      </c>
+      <c r="T14" t="str">
         <v/>
       </c>
     </row>
@@ -2512,28 +4096,28 @@
         <v>602</v>
       </c>
       <c r="D15" t="str">
-        <v>+961 3 800 428</v>
+        <v>+961 3 537 292</v>
       </c>
       <c r="E15" t="str">
-        <v>today+120d-12m</v>
+        <v>today+82d-12m</v>
       </c>
       <c r="F15" t="str">
-        <v>today+120d</v>
+        <v>today+82d</v>
       </c>
       <c r="G15">
-        <v>1000</v>
+        <v>1075</v>
       </c>
       <c r="H15">
-        <v>1000</v>
+        <v>1075</v>
       </c>
       <c r="I15">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="J15" t="str">
-        <v>cash</v>
+        <v>monthly</v>
       </c>
       <c r="K15" t="str">
-        <v/>
+        <v>cheque</v>
       </c>
       <c r="L15" t="str">
         <v/>
@@ -2542,87 +4126,39 @@
         <v/>
       </c>
       <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <v/>
+      </c>
+      <c r="P15" t="str">
+        <v/>
+      </c>
+      <c r="Q15" t="str">
+        <v/>
+      </c>
+      <c r="R15" t="str">
+        <v/>
+      </c>
+      <c r="S15" t="str">
+        <v/>
+      </c>
+      <c r="T15" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T15"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:I15"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="17.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>tenant_phone</v>
-      </c>
-      <c r="B1" t="str">
-        <v>kind</v>
-      </c>
-      <c r="C1" t="str">
-        <v>title</v>
-      </c>
-      <c r="D1" t="str">
-        <v>file_name</v>
-      </c>
-      <c r="E1" t="str">
-        <v>contract_number</v>
-      </c>
-      <c r="F1" t="str">
-        <v>issued_date</v>
-      </c>
-      <c r="G1" t="str">
-        <v>expiry_date</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>+961 70 108 759</v>
-      </c>
-      <c r="B2" t="str">
-        <v>id</v>
-      </c>
-      <c r="C2" t="str">
-        <v>National ID</v>
-      </c>
-      <c r="D2" t="str">
-        <v>antoine-baydoun-id.pdf</v>
-      </c>
-      <c r="E2" t="str">
-        <v/>
-      </c>
-      <c r="F2" t="str">
-        <v>today-5y</v>
-      </c>
-      <c r="G2" t="str">
-        <v>today+2y</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1"/>
-  <cols>
-    <col min="1" max="1" width="17.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
     <col min="3" max="3" width="14.83203125" customWidth="1"/>
     <col min="4" max="4" width="14.83203125" customWidth="1"/>
@@ -2630,37 +4166,1410 @@
     <col min="6" max="6" width="14.83203125" customWidth="1"/>
     <col min="7" max="7" width="14.83203125" customWidth="1"/>
     <col min="8" max="8" width="14.83203125" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>contract_number</v>
+        <v>name</v>
       </c>
       <c r="B1" t="str">
-        <v>period</v>
+        <v>category</v>
       </c>
       <c r="C1" t="str">
-        <v>due_date</v>
+        <v>phone</v>
       </c>
       <c r="D1" t="str">
-        <v>amount_due</v>
+        <v>email</v>
       </c>
       <c r="E1" t="str">
-        <v>amount_paid</v>
+        <v>company</v>
       </c>
       <c r="F1" t="str">
-        <v>paid_date</v>
+        <v>services</v>
       </c>
       <c r="G1" t="str">
-        <v>method</v>
+        <v>rating</v>
       </c>
       <c r="H1" t="str">
-        <v>reference</v>
+        <v>active</v>
+      </c>
+      <c r="I1" t="str">
+        <v>notes</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Schindler Lebanon</v>
+      </c>
+      <c r="B2" t="str">
+        <v>elevator</v>
+      </c>
+      <c r="C2" t="str">
+        <v>+961 1 500 200</v>
+      </c>
+      <c r="D2" t="str">
+        <v>schindler.lebanon@example.com</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Schindler</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Elevator maintenance, inspections, modernisation</v>
+      </c>
+      <c r="G2">
+        <v>4.5</v>
+      </c>
+      <c r="H2" t="str">
+        <v>yes</v>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Elevatech</v>
+      </c>
+      <c r="B3" t="str">
+        <v>elevator</v>
+      </c>
+      <c r="C3" t="str">
+        <v>+961 1 388 110</v>
+      </c>
+      <c r="D3" t="str">
+        <v>elevatech@example.com</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v>Elevator repairs</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3" t="str">
+        <v>yes</v>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Nakhle Electric</v>
+      </c>
+      <c r="B4" t="str">
+        <v>electrical</v>
+      </c>
+      <c r="C4" t="str">
+        <v>+961 3 410 220</v>
+      </c>
+      <c r="D4" t="str">
+        <v>nakhle.electric@example.com</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v>Electrical repairs, panels, lighting</v>
+      </c>
+      <c r="G4">
+        <v>4</v>
+      </c>
+      <c r="H4" t="str">
+        <v>yes</v>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Abou Rjeily Plumbing</v>
+      </c>
+      <c r="B5" t="str">
+        <v>plumbing</v>
+      </c>
+      <c r="C5" t="str">
+        <v>+961 3 900 100</v>
+      </c>
+      <c r="D5" t="str">
+        <v>abou.rjeily.plumbing@example.com</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v>Plumbing, leaks, water heaters</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5" t="str">
+        <v>yes</v>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Khalil &amp; Sons Plumbing</v>
+      </c>
+      <c r="B6" t="str">
+        <v>plumbing</v>
+      </c>
+      <c r="C6" t="str">
+        <v>+961 70 880 330</v>
+      </c>
+      <c r="D6" t="str">
+        <v>khalil.sons.plumbing@example.com</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Khalil &amp; Sons</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Plumbing, drainage, bathrooms</v>
+      </c>
+      <c r="G6">
+        <v>4.5</v>
+      </c>
+      <c r="H6" t="str">
+        <v>yes</v>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>CoolAir HVAC</v>
+      </c>
+      <c r="B7" t="str">
+        <v>hvac</v>
+      </c>
+      <c r="C7" t="str">
+        <v>+961 71 640 555</v>
+      </c>
+      <c r="D7" t="str">
+        <v>coolair.hvac@example.com</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v>Air conditioning, ventilation, chillers</v>
+      </c>
+      <c r="G7">
+        <v>4</v>
+      </c>
+      <c r="H7" t="str">
+        <v>yes</v>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>PowerGen Services</v>
+      </c>
+      <c r="B8" t="str">
+        <v>generator</v>
+      </c>
+      <c r="C8" t="str">
+        <v>+961 3 222 909</v>
+      </c>
+      <c r="D8" t="str">
+        <v>powergen.services@example.com</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v>Generator maintenance, fuel, repairs</v>
+      </c>
+      <c r="G8">
+        <v>3.5</v>
+      </c>
+      <c r="H8" t="str">
+        <v>yes</v>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Bright Clean Co.</v>
+      </c>
+      <c r="B9" t="str">
+        <v>cleaning</v>
+      </c>
+      <c r="C9" t="str">
+        <v>+961 76 300 400</v>
+      </c>
+      <c r="D9" t="str">
+        <v>bright.clean.co.@example.com</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v>Common-area cleaning, glass, deep cleaning</v>
+      </c>
+      <c r="G9">
+        <v>4</v>
+      </c>
+      <c r="H9" t="str">
+        <v>yes</v>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>SecureWatch</v>
+      </c>
+      <c r="B10" t="str">
+        <v>security</v>
+      </c>
+      <c r="C10" t="str">
+        <v>+961 1 770 700</v>
+      </c>
+      <c r="D10" t="str">
+        <v>securewatch@example.com</v>
+      </c>
+      <c r="E10" t="str">
+        <v>SecureWatch SAL</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Guards, CCTV, access control</v>
+      </c>
+      <c r="G10">
+        <v>3.5</v>
+      </c>
+      <c r="H10" t="str">
+        <v>yes</v>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Beirut Painters</v>
+      </c>
+      <c r="B11" t="str">
+        <v>painting</v>
+      </c>
+      <c r="C11" t="str">
+        <v>+961 78 121 121</v>
+      </c>
+      <c r="D11" t="str">
+        <v>beirut.painters@example.com</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v>Painting, plastering, waterproofing</v>
+      </c>
+      <c r="G11">
+        <v>4</v>
+      </c>
+      <c r="H11" t="str">
+        <v>yes</v>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>PestAway</v>
+      </c>
+      <c r="B12" t="str">
+        <v>pest_control</v>
+      </c>
+      <c r="C12" t="str">
+        <v>+961 70 555 777</v>
+      </c>
+      <c r="D12" t="str">
+        <v>pestaway@example.com</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v>Pest control, fumigation</v>
+      </c>
+      <c r="G12">
+        <v>4</v>
+      </c>
+      <c r="H12" t="str">
+        <v>yes</v>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Metn Contractors</v>
+      </c>
+      <c r="B13" t="str">
+        <v>general_contractor</v>
+      </c>
+      <c r="C13" t="str">
+        <v>+961 3 656 656</v>
+      </c>
+      <c r="D13" t="str">
+        <v>metn.contractors@example.com</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Metn Contractors SARL</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Renovations, structural works, kitchens</v>
+      </c>
+      <c r="G13">
+        <v>3.5</v>
+      </c>
+      <c r="H13" t="str">
+        <v>yes</v>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>AquaTank Services</v>
+      </c>
+      <c r="B14" t="str">
+        <v>other</v>
+      </c>
+      <c r="C14" t="str">
+        <v>+961 71 909 111</v>
+      </c>
+      <c r="D14" t="str">
+        <v>aquatank.services@example.com</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v>Water tank cleaning, pumps</v>
+      </c>
+      <c r="G14">
+        <v>4</v>
+      </c>
+      <c r="H14" t="str">
+        <v>yes</v>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>FireSafe Lebanon</v>
+      </c>
+      <c r="B15" t="str">
+        <v>other</v>
+      </c>
+      <c r="C15" t="str">
+        <v>+961 1 234 567</v>
+      </c>
+      <c r="D15" t="str">
+        <v>firesafe.lebanon@example.com</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v>Fire systems, extinguishers, certification</v>
+      </c>
+      <c r="G15">
+        <v>4.5</v>
+      </c>
+      <c r="H15" t="str">
+        <v>yes</v>
+      </c>
+      <c r="I15" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I15"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:O9"/>
+  <cols>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" customWidth="1"/>
+    <col min="8" max="8" width="19.83203125" customWidth="1"/>
+    <col min="9" max="9" width="15.83203125" customWidth="1"/>
+    <col min="10" max="10" width="17.83203125" customWidth="1"/>
+    <col min="11" max="11" width="15.83203125" customWidth="1"/>
+    <col min="12" max="12" width="14.83203125" customWidth="1"/>
+    <col min="13" max="13" width="19.83203125" customWidth="1"/>
+    <col min="14" max="14" width="14.83203125" customWidth="1"/>
+    <col min="15" max="15" width="14.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>property_code</v>
+      </c>
+      <c r="B1" t="str">
+        <v>unit_number</v>
+      </c>
+      <c r="C1" t="str">
+        <v>asset_type</v>
+      </c>
+      <c r="D1" t="str">
+        <v>name</v>
+      </c>
+      <c r="E1" t="str">
+        <v>manufacturer</v>
+      </c>
+      <c r="F1" t="str">
+        <v>model</v>
+      </c>
+      <c r="G1" t="str">
+        <v>serial_number</v>
+      </c>
+      <c r="H1" t="str">
+        <v>installation_date</v>
+      </c>
+      <c r="I1" t="str">
+        <v>purchase_cost</v>
+      </c>
+      <c r="J1" t="str">
+        <v>warranty_expiry</v>
+      </c>
+      <c r="K1" t="str">
+        <v>supplier_name</v>
+      </c>
+      <c r="L1" t="str">
+        <v>status</v>
+      </c>
+      <c r="M1" t="str">
+        <v>last_service_date</v>
+      </c>
+      <c r="N1" t="str">
+        <v>qr_code</v>
+      </c>
+      <c r="O1" t="str">
+        <v>notes</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>CR</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v>elevator</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Elevator 1</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Schindler</v>
+      </c>
+      <c r="F2" t="str">
+        <v>3300</v>
+      </c>
+      <c r="G2" t="str">
+        <v>SCH-382101</v>
+      </c>
+      <c r="H2" t="str">
+        <v>2017-09-14</v>
+      </c>
+      <c r="I2">
+        <v>48000</v>
+      </c>
+      <c r="J2" t="str">
+        <v>today-29m</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Schindler Lebanon</v>
+      </c>
+      <c r="L2" t="str">
+        <v>operational</v>
+      </c>
+      <c r="M2" t="str">
+        <v>today-75d</v>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>CR</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v>generator</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Generator</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Perkins</v>
+      </c>
+      <c r="F3" t="str">
+        <v>P387</v>
+      </c>
+      <c r="G3" t="str">
+        <v>PER-472804</v>
+      </c>
+      <c r="H3" t="str">
+        <v>2017-08-25</v>
+      </c>
+      <c r="I3">
+        <v>32000</v>
+      </c>
+      <c r="J3" t="str">
+        <v>today-17m</v>
+      </c>
+      <c r="K3" t="str">
+        <v>PowerGen Services</v>
+      </c>
+      <c r="L3" t="str">
+        <v>operational</v>
+      </c>
+      <c r="M3" t="str">
+        <v>today-135d</v>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>CR</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v>water_pump</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Water pump</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Grundfos</v>
+      </c>
+      <c r="F4" t="str">
+        <v>CR 10</v>
+      </c>
+      <c r="G4" t="str">
+        <v>GRU-159495</v>
+      </c>
+      <c r="H4" t="str">
+        <v>2017-10-05</v>
+      </c>
+      <c r="I4">
+        <v>4200</v>
+      </c>
+      <c r="J4" t="str">
+        <v>today-28m</v>
+      </c>
+      <c r="K4" t="str">
+        <v>AquaTank Services</v>
+      </c>
+      <c r="L4" t="str">
+        <v>operational</v>
+      </c>
+      <c r="M4" t="str">
+        <v>today-44d</v>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>CR</v>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v>water_tank</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Roof water tank</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Sidem</v>
+      </c>
+      <c r="F5" t="str">
+        <v>10m³</v>
+      </c>
+      <c r="G5" t="str">
+        <v>SID-959334</v>
+      </c>
+      <c r="H5" t="str">
+        <v>2017-02-19</v>
+      </c>
+      <c r="I5">
+        <v>3800</v>
+      </c>
+      <c r="J5" t="str">
+        <v>today-25m</v>
+      </c>
+      <c r="K5" t="str">
+        <v>AquaTank Services</v>
+      </c>
+      <c r="L5" t="str">
+        <v>operational</v>
+      </c>
+      <c r="M5" t="str">
+        <v>today-65d</v>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>CR</v>
+      </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
+      <c r="C6" t="str">
+        <v>fire_system</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Fire alarm &amp; extinguishers</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Honeywell</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Notifier</v>
+      </c>
+      <c r="G6" t="str">
+        <v>HON-691829</v>
+      </c>
+      <c r="H6" t="str">
+        <v>2022-09-13</v>
+      </c>
+      <c r="I6">
+        <v>9500</v>
+      </c>
+      <c r="J6" t="str">
+        <v>today+29m</v>
+      </c>
+      <c r="K6" t="str">
+        <v>FireSafe Lebanon</v>
+      </c>
+      <c r="L6" t="str">
+        <v>operational</v>
+      </c>
+      <c r="M6" t="str">
+        <v>today-82d</v>
+      </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>CR</v>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v>cctv</v>
+      </c>
+      <c r="D7" t="str">
+        <v>CCTV system</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Hikvision</v>
+      </c>
+      <c r="F7" t="str">
+        <v>DS-7616</v>
+      </c>
+      <c r="G7" t="str">
+        <v>HIK-871507</v>
+      </c>
+      <c r="H7" t="str">
+        <v>2020-09-19</v>
+      </c>
+      <c r="I7">
+        <v>3200</v>
+      </c>
+      <c r="J7" t="str">
+        <v>today-18m</v>
+      </c>
+      <c r="K7" t="str">
+        <v>SecureWatch</v>
+      </c>
+      <c r="L7" t="str">
+        <v>operational</v>
+      </c>
+      <c r="M7" t="str">
+        <v>today-115d</v>
+      </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>CR</v>
+      </c>
+      <c r="B8" t="str">
+        <v/>
+      </c>
+      <c r="C8" t="str">
+        <v>electrical_panel</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Main electrical panel</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Schneider</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Prisma</v>
+      </c>
+      <c r="G8" t="str">
+        <v>SCH-754588</v>
+      </c>
+      <c r="H8" t="str">
+        <v>2017-02-04</v>
+      </c>
+      <c r="I8">
+        <v>6800</v>
+      </c>
+      <c r="J8" t="str">
+        <v>today+29m</v>
+      </c>
+      <c r="K8" t="str">
+        <v>Nakhle Electric</v>
+      </c>
+      <c r="L8" t="str">
+        <v>operational</v>
+      </c>
+      <c r="M8" t="str">
+        <v>today-136d</v>
+      </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>CR</v>
+      </c>
+      <c r="B9" t="str">
+        <v/>
+      </c>
+      <c r="C9" t="str">
+        <v>parking_gate</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Parking gate</v>
+      </c>
+      <c r="E9" t="str">
+        <v>CAME</v>
+      </c>
+      <c r="F9" t="str">
+        <v>BX-74</v>
+      </c>
+      <c r="G9" t="str">
+        <v>CAM-310880</v>
+      </c>
+      <c r="H9" t="str">
+        <v>2017-03-15</v>
+      </c>
+      <c r="I9">
+        <v>2400</v>
+      </c>
+      <c r="J9" t="str">
+        <v>today+14m</v>
+      </c>
+      <c r="K9" t="str">
+        <v>SecureWatch</v>
+      </c>
+      <c r="L9" t="str">
+        <v>operational</v>
+      </c>
+      <c r="M9" t="str">
+        <v>today-75d</v>
+      </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:O9"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:V1"/>
+  <cols>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
+    <col min="10" max="10" width="14.83203125" customWidth="1"/>
+    <col min="11" max="11" width="14.83203125" customWidth="1"/>
+    <col min="12" max="12" width="14.83203125" customWidth="1"/>
+    <col min="13" max="13" width="15.83203125" customWidth="1"/>
+    <col min="14" max="14" width="16.83203125" customWidth="1"/>
+    <col min="15" max="15" width="14.83203125" customWidth="1"/>
+    <col min="16" max="16" width="19.83203125" customWidth="1"/>
+    <col min="17" max="17" width="14.83203125" customWidth="1"/>
+    <col min="18" max="18" width="14.83203125" customWidth="1"/>
+    <col min="19" max="19" width="14.83203125" customWidth="1"/>
+    <col min="20" max="20" width="14.83203125" customWidth="1"/>
+    <col min="21" max="21" width="18.83203125" customWidth="1"/>
+    <col min="22" max="22" width="14.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>number</v>
+      </c>
+      <c r="B1" t="str">
+        <v>property_code</v>
+      </c>
+      <c r="C1" t="str">
+        <v>unit_number</v>
+      </c>
+      <c r="D1" t="str">
+        <v>asset_name</v>
+      </c>
+      <c r="E1" t="str">
+        <v>tenant_phone</v>
+      </c>
+      <c r="F1" t="str">
+        <v>title</v>
+      </c>
+      <c r="G1" t="str">
+        <v>description</v>
+      </c>
+      <c r="H1" t="str">
+        <v>category</v>
+      </c>
+      <c r="I1" t="str">
+        <v>priority</v>
+      </c>
+      <c r="J1" t="str">
+        <v>status</v>
+      </c>
+      <c r="K1" t="str">
+        <v>source</v>
+      </c>
+      <c r="L1" t="str">
+        <v>reported_at</v>
+      </c>
+      <c r="M1" t="str">
+        <v>supplier_name</v>
+      </c>
+      <c r="N1" t="str">
+        <v>estimated_cost</v>
+      </c>
+      <c r="O1" t="str">
+        <v>actual_cost</v>
+      </c>
+      <c r="P1" t="str">
+        <v>approval_required</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>approved_at</v>
+      </c>
+      <c r="R1" t="str">
+        <v>started_at</v>
+      </c>
+      <c r="S1" t="str">
+        <v>completed_at</v>
+      </c>
+      <c r="T1" t="str">
+        <v>closed_at</v>
+      </c>
+      <c r="U1" t="str">
+        <v>repeat_of_number</v>
+      </c>
+      <c r="V1" t="str">
+        <v>notes</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:V1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K11"/>
+  <cols>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" customWidth="1"/>
+    <col min="4" max="4" width="19.83203125" customWidth="1"/>
+    <col min="5" max="5" width="19.83203125" customWidth="1"/>
+    <col min="6" max="6" width="19.83203125" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" customWidth="1"/>
+    <col min="8" max="8" width="16.83203125" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
+    <col min="10" max="10" width="15.83203125" customWidth="1"/>
+    <col min="11" max="11" width="14.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>property_code</v>
+      </c>
+      <c r="B1" t="str">
+        <v>asset_name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>maintenance_type</v>
+      </c>
+      <c r="D1" t="str">
+        <v>recurrence_months</v>
+      </c>
+      <c r="E1" t="str">
+        <v>last_service_date</v>
+      </c>
+      <c r="F1" t="str">
+        <v>next_service_date</v>
+      </c>
+      <c r="G1" t="str">
+        <v>supplier_name</v>
+      </c>
+      <c r="H1" t="str">
+        <v>estimated_cost</v>
+      </c>
+      <c r="I1" t="str">
+        <v>status</v>
+      </c>
+      <c r="J1" t="str">
+        <v>reminder_days</v>
+      </c>
+      <c r="K1" t="str">
+        <v>notes</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>CR</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Elevator 1</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Elevator service</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2" t="str">
+        <v>today-12d</v>
+      </c>
+      <c r="F2" t="str">
+        <v>today+78d</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Schindler Lebanon</v>
+      </c>
+      <c r="H2">
+        <v>350</v>
+      </c>
+      <c r="I2" t="str">
+        <v>active</v>
+      </c>
+      <c r="J2">
+        <v>14</v>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>CR</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Elevator 1</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Elevator safety certification</v>
+      </c>
+      <c r="D3">
+        <v>12</v>
+      </c>
+      <c r="E3" t="str">
+        <v>today-235d</v>
+      </c>
+      <c r="F3" t="str">
+        <v>today+125d</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Schindler Lebanon</v>
+      </c>
+      <c r="H3">
+        <v>600</v>
+      </c>
+      <c r="I3" t="str">
+        <v>active</v>
+      </c>
+      <c r="J3">
+        <v>14</v>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>CR</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Generator</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Generator service</v>
+      </c>
+      <c r="D4">
+        <v>6</v>
+      </c>
+      <c r="E4" t="str">
+        <v>today-52d</v>
+      </c>
+      <c r="F4" t="str">
+        <v>today+128d</v>
+      </c>
+      <c r="G4" t="str">
+        <v>PowerGen Services</v>
+      </c>
+      <c r="H4">
+        <v>400</v>
+      </c>
+      <c r="I4" t="str">
+        <v>active</v>
+      </c>
+      <c r="J4">
+        <v>14</v>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>CR</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Water pump</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Pump inspection</v>
+      </c>
+      <c r="D5">
+        <v>6</v>
+      </c>
+      <c r="E5" t="str">
+        <v>today-95d</v>
+      </c>
+      <c r="F5" t="str">
+        <v>today+85d</v>
+      </c>
+      <c r="G5" t="str">
+        <v>AquaTank Services</v>
+      </c>
+      <c r="H5">
+        <v>120</v>
+      </c>
+      <c r="I5" t="str">
+        <v>active</v>
+      </c>
+      <c r="J5">
+        <v>14</v>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>CR</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Roof water tank</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Tank cleaning</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6" t="str">
+        <v>today-162d</v>
+      </c>
+      <c r="F6" t="str">
+        <v>today+18d</v>
+      </c>
+      <c r="G6" t="str">
+        <v>AquaTank Services</v>
+      </c>
+      <c r="H6">
+        <v>180</v>
+      </c>
+      <c r="I6" t="str">
+        <v>active</v>
+      </c>
+      <c r="J6">
+        <v>14</v>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>CR</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Fire alarm &amp; extinguishers</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Fire system inspection</v>
+      </c>
+      <c r="D7">
+        <v>12</v>
+      </c>
+      <c r="E7" t="str">
+        <v>today-317d</v>
+      </c>
+      <c r="F7" t="str">
+        <v>today+43d</v>
+      </c>
+      <c r="G7" t="str">
+        <v>FireSafe Lebanon</v>
+      </c>
+      <c r="H7">
+        <v>450</v>
+      </c>
+      <c r="I7" t="str">
+        <v>active</v>
+      </c>
+      <c r="J7">
+        <v>14</v>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>CR</v>
+      </c>
+      <c r="B8" t="str">
+        <v>CCTV system</v>
+      </c>
+      <c r="C8" t="str">
+        <v>CCTV check</v>
+      </c>
+      <c r="D8">
+        <v>12</v>
+      </c>
+      <c r="E8" t="str">
+        <v>today-271d</v>
+      </c>
+      <c r="F8" t="str">
+        <v>today+89d</v>
+      </c>
+      <c r="G8" t="str">
+        <v>SecureWatch</v>
+      </c>
+      <c r="H8">
+        <v>150</v>
+      </c>
+      <c r="I8" t="str">
+        <v>active</v>
+      </c>
+      <c r="J8">
+        <v>14</v>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>CR</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Main electrical panel</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Panel thermal inspection</v>
+      </c>
+      <c r="D9">
+        <v>12</v>
+      </c>
+      <c r="E9" t="str">
+        <v>today-174d</v>
+      </c>
+      <c r="F9" t="str">
+        <v>today+186d</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Nakhle Electric</v>
+      </c>
+      <c r="H9">
+        <v>200</v>
+      </c>
+      <c r="I9" t="str">
+        <v>active</v>
+      </c>
+      <c r="J9">
+        <v>14</v>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>CR</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Parking gate</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Gate motor service</v>
+      </c>
+      <c r="D10">
+        <v>12</v>
+      </c>
+      <c r="E10" t="str">
+        <v>today-204d</v>
+      </c>
+      <c r="F10" t="str">
+        <v>today+156d</v>
+      </c>
+      <c r="G10" t="str">
+        <v>SecureWatch</v>
+      </c>
+      <c r="H10">
+        <v>120</v>
+      </c>
+      <c r="I10" t="str">
+        <v>active</v>
+      </c>
+      <c r="J10">
+        <v>14</v>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>CR</v>
+      </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
+      <c r="C11" t="str">
+        <v>Pest control treatment</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11" t="str">
+        <v>today-79d</v>
+      </c>
+      <c r="F11" t="str">
+        <v>today+17d</v>
+      </c>
+      <c r="G11" t="str">
+        <v>PestAway</v>
+      </c>
+      <c r="H11">
+        <v>120</v>
+      </c>
+      <c r="I11" t="str">
+        <v>active</v>
+      </c>
+      <c r="J11">
+        <v>7</v>
+      </c>
+      <c r="K11" t="str">
+        <v>Common areas and garbage room</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:K11"/>
   </ignoredErrors>
 </worksheet>
 </file>